--- a/templates/excel/Format CC3.xlsx
+++ b/templates/excel/Format CC3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github-desktop\UI\QA\CA-Dev-New\backend\templates\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CA-DEV\CA-BACKEND-DEV\templates\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4238BAA8-80F8-4844-B9B9-83EB95F2B435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DBD5F1-CCAE-46BD-9DC6-3E231A7370A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions.1" sheetId="26" r:id="rId1"/>
@@ -2390,7 +2390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="378">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3006,6 +3006,69 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="30" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="30" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3015,6 +3078,24 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3033,86 +3114,14 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="30" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="30" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3123,39 +3132,30 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3236,6 +3236,20 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4160,31 +4174,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T197"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7265625" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="68.453125" style="90" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="68.44140625" style="90" customWidth="1"/>
     <col min="4" max="4" width="29" style="101" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" style="101" customWidth="1"/>
-    <col min="6" max="6" width="57.26953125" style="101" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.81640625" style="101" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" customWidth="1"/>
-    <col min="9" max="9" width="34.7265625" style="101" customWidth="1"/>
-    <col min="10" max="10" width="24.81640625" customWidth="1"/>
-    <col min="11" max="11" width="8.1796875" customWidth="1"/>
-    <col min="12" max="12" width="32.453125" customWidth="1"/>
-    <col min="13" max="13" width="10.7265625" customWidth="1"/>
-    <col min="14" max="14" width="13.54296875" customWidth="1"/>
-    <col min="15" max="15" width="12.7265625" customWidth="1"/>
-    <col min="16" max="16" width="11.1796875" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="101" customWidth="1"/>
+    <col min="6" max="6" width="57.21875" style="101" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.77734375" style="101" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="34.77734375" style="101" customWidth="1"/>
+    <col min="10" max="10" width="24.77734375" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" customWidth="1"/>
+    <col min="12" max="12" width="32.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" customWidth="1"/>
+    <col min="15" max="15" width="12.77734375" customWidth="1"/>
+    <col min="16" max="16" width="11.21875" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="19" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:17" ht="52" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:17" ht="52.8" x14ac:dyDescent="0.25">
       <c r="B2" s="109" t="s">
         <v>140</v>
       </c>
@@ -4219,7 +4233,7 @@
       <c r="P2" s="90"/>
       <c r="Q2" s="90"/>
     </row>
-    <row r="3" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="109"/>
       <c r="C3" s="109"/>
       <c r="D3" s="110"/>
@@ -4236,8 +4250,8 @@
       <c r="P3" s="90"/>
       <c r="Q3" s="90"/>
     </row>
-    <row r="4" spans="2:17" ht="14" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="330" t="s">
+    <row r="4" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="308" t="s">
         <v>154</v>
       </c>
       <c r="C4" s="151" t="s">
@@ -4261,8 +4275,8 @@
       <c r="P4" s="90"/>
       <c r="Q4" s="90"/>
     </row>
-    <row r="5" spans="2:17" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="331"/>
+    <row r="5" spans="2:17" ht="14.4" x14ac:dyDescent="0.35">
+      <c r="B5" s="309"/>
       <c r="C5" s="234" t="s">
         <v>237</v>
       </c>
@@ -4286,8 +4300,8 @@
       <c r="P5" s="90"/>
       <c r="Q5" s="90"/>
     </row>
-    <row r="6" spans="2:17" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="332"/>
+    <row r="6" spans="2:17" ht="14.4" x14ac:dyDescent="0.35">
+      <c r="B6" s="310"/>
       <c r="C6" s="105" t="s">
         <v>103</v>
       </c>
@@ -4309,8 +4323,8 @@
       <c r="P6" s="90"/>
       <c r="Q6" s="90"/>
     </row>
-    <row r="7" spans="2:17" ht="14" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="332"/>
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="310"/>
       <c r="C7" s="108" t="s">
         <v>104</v>
       </c>
@@ -4332,8 +4346,8 @@
       <c r="P7" s="90"/>
       <c r="Q7" s="90"/>
     </row>
-    <row r="8" spans="2:17" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="333"/>
+    <row r="8" spans="2:17" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="B8" s="311"/>
       <c r="C8" s="174" t="s">
         <v>148</v>
       </c>
@@ -4357,8 +4371,8 @@
       <c r="P8" s="90"/>
       <c r="Q8" s="90"/>
     </row>
-    <row r="9" spans="2:17" ht="14" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="333"/>
+    <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="311"/>
       <c r="C9" s="174" t="s">
         <v>126</v>
       </c>
@@ -4380,7 +4394,7 @@
       <c r="P9" s="90"/>
       <c r="Q9" s="90"/>
     </row>
-    <row r="10" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="187"/>
       <c r="C10" s="188"/>
       <c r="D10" s="189"/>
@@ -4397,8 +4411,8 @@
       <c r="P10" s="90"/>
       <c r="Q10" s="90"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="331" t="s">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="309" t="s">
         <v>153</v>
       </c>
       <c r="C11" s="184" t="s">
@@ -4424,8 +4438,8 @@
       <c r="P11" s="90"/>
       <c r="Q11" s="90"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="332"/>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="310"/>
       <c r="C12" s="180" t="s">
         <v>195</v>
       </c>
@@ -4449,8 +4463,8 @@
       <c r="P12" s="90"/>
       <c r="Q12" s="90"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="332"/>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="310"/>
       <c r="C13" s="180" t="s">
         <v>97</v>
       </c>
@@ -4477,8 +4491,8 @@
       <c r="P13" s="90"/>
       <c r="Q13" s="90"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="332"/>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="310"/>
       <c r="C14" s="180" t="s">
         <v>174</v>
       </c>
@@ -4505,8 +4519,8 @@
       <c r="P14" s="90"/>
       <c r="Q14" s="90"/>
     </row>
-    <row r="15" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="333"/>
+    <row r="15" spans="2:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="311"/>
       <c r="C15" s="182" t="s">
         <v>107</v>
       </c>
@@ -4535,7 +4549,7 @@
       <c r="P15" s="90"/>
       <c r="Q15" s="90"/>
     </row>
-    <row r="16" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="187"/>
       <c r="C16" s="188"/>
       <c r="D16" s="189"/>
@@ -4552,8 +4566,8 @@
       <c r="P16" s="90"/>
       <c r="Q16" s="90"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="334" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B17" s="312" t="s">
         <v>196</v>
       </c>
       <c r="C17" s="184" t="s">
@@ -4574,18 +4588,18 @@
       <c r="J17" s="216" t="s">
         <v>210</v>
       </c>
-      <c r="K17" s="323" t="s">
+      <c r="K17" s="301" t="s">
         <v>175</v>
       </c>
-      <c r="L17" s="324"/>
+      <c r="L17" s="302"/>
       <c r="M17" s="90"/>
       <c r="N17" s="91"/>
       <c r="O17" s="90"/>
       <c r="P17" s="90"/>
       <c r="Q17" s="90"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B18" s="334"/>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B18" s="312"/>
       <c r="C18" s="105" t="s">
         <v>150</v>
       </c>
@@ -4611,8 +4625,8 @@
       <c r="P18" s="90"/>
       <c r="Q18" s="90"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B19" s="334"/>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B19" s="312"/>
       <c r="C19" s="105" t="s">
         <v>151</v>
       </c>
@@ -4638,8 +4652,8 @@
       <c r="P19" s="90"/>
       <c r="Q19" s="90"/>
     </row>
-    <row r="20" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="334"/>
+    <row r="20" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="312"/>
       <c r="C20" s="192" t="s">
         <v>152</v>
       </c>
@@ -4664,7 +4678,7 @@
       <c r="P20" s="90"/>
       <c r="Q20" s="90"/>
     </row>
-    <row r="21" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="90"/>
       <c r="B21" s="187"/>
       <c r="C21" s="188">
@@ -4681,7 +4695,7 @@
       <c r="L21" s="90"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="335" t="s">
+      <c r="B22" s="313" t="s">
         <v>211</v>
       </c>
       <c r="C22" s="199" t="s">
@@ -4705,7 +4719,7 @@
       <c r="Q22" s="153"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="335"/>
+      <c r="B23" s="313"/>
       <c r="C23" s="200" t="s">
         <v>1</v>
       </c>
@@ -4727,10 +4741,10 @@
       <c r="Q23" s="153"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="325" t="s">
+      <c r="A24" s="303" t="s">
         <v>212</v>
       </c>
-      <c r="B24" s="335"/>
+      <c r="B24" s="313"/>
       <c r="C24" s="200" t="s">
         <v>93</v>
       </c>
@@ -4755,8 +4769,8 @@
       <c r="Q24" s="153"/>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="325"/>
-      <c r="B25" s="335"/>
+      <c r="A25" s="303"/>
+      <c r="B25" s="313"/>
       <c r="C25" s="200" t="s">
         <v>2</v>
       </c>
@@ -4778,8 +4792,8 @@
       <c r="Q25" s="153"/>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="325"/>
-      <c r="B26" s="335"/>
+      <c r="A26" s="303"/>
+      <c r="B26" s="313"/>
       <c r="C26" s="200" t="s">
         <v>184</v>
       </c>
@@ -4801,7 +4815,7 @@
       <c r="Q26" s="153"/>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="335"/>
+      <c r="B27" s="313"/>
       <c r="C27" s="200" t="s">
         <v>69</v>
       </c>
@@ -4823,7 +4837,7 @@
       <c r="Q27" s="153"/>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="335"/>
+      <c r="B28" s="313"/>
       <c r="C28" s="200" t="s">
         <v>33</v>
       </c>
@@ -4845,7 +4859,7 @@
       <c r="Q28" s="153"/>
     </row>
     <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="335"/>
+      <c r="B29" s="313"/>
       <c r="C29" s="200" t="s">
         <v>157</v>
       </c>
@@ -4867,7 +4881,7 @@
       <c r="Q29" s="153"/>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="335"/>
+      <c r="B30" s="313"/>
       <c r="C30" s="200" t="s">
         <v>70</v>
       </c>
@@ -4889,7 +4903,7 @@
       <c r="Q30" s="153"/>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="335"/>
+      <c r="B31" s="313"/>
       <c r="C31" s="201" t="s">
         <v>130</v>
       </c>
@@ -4911,7 +4925,7 @@
       <c r="Q31" s="153"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="335"/>
+      <c r="B32" s="313"/>
       <c r="C32" s="200" t="s">
         <v>232</v>
       </c>
@@ -4932,8 +4946,8 @@
       <c r="P32" s="153"/>
       <c r="Q32" s="153"/>
     </row>
-    <row r="33" spans="2:17" ht="14" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="335"/>
+    <row r="33" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="313"/>
       <c r="C33" s="202" t="s">
         <v>233</v>
       </c>
@@ -4958,7 +4972,7 @@
       <c r="Q33" s="153"/>
     </row>
     <row r="34" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="335"/>
+      <c r="B34" s="313"/>
       <c r="C34" s="203" t="s">
         <v>185</v>
       </c>
@@ -4980,7 +4994,7 @@
       <c r="Q34" s="153"/>
     </row>
     <row r="35" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="335"/>
+      <c r="B35" s="313"/>
       <c r="C35" s="201" t="s">
         <v>186</v>
       </c>
@@ -5002,7 +5016,7 @@
       <c r="Q35" s="153"/>
     </row>
     <row r="36" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="335"/>
+      <c r="B36" s="313"/>
       <c r="C36" s="201" t="s">
         <v>187</v>
       </c>
@@ -5024,7 +5038,7 @@
       <c r="Q36" s="153"/>
     </row>
     <row r="37" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="335"/>
+      <c r="B37" s="313"/>
       <c r="C37" s="201" t="s">
         <v>189</v>
       </c>
@@ -5051,7 +5065,7 @@
       <c r="Q37" s="153"/>
     </row>
     <row r="38" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="335"/>
+      <c r="B38" s="313"/>
       <c r="C38" s="201" t="s">
         <v>33</v>
       </c>
@@ -5076,7 +5090,7 @@
       <c r="Q38" s="153"/>
     </row>
     <row r="39" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="335"/>
+      <c r="B39" s="313"/>
       <c r="C39" s="201" t="s">
         <v>188</v>
       </c>
@@ -5101,7 +5115,7 @@
       <c r="Q39" s="153"/>
     </row>
     <row r="40" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="335"/>
+      <c r="B40" s="313"/>
       <c r="C40" s="201" t="s">
         <v>190</v>
       </c>
@@ -5123,7 +5137,7 @@
       <c r="Q40" s="153"/>
     </row>
     <row r="41" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="335"/>
+      <c r="B41" s="313"/>
       <c r="C41" s="201" t="s">
         <v>4</v>
       </c>
@@ -5145,7 +5159,7 @@
       <c r="Q41" s="153"/>
     </row>
     <row r="42" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="335"/>
+      <c r="B42" s="313"/>
       <c r="C42" s="201" t="s">
         <v>66</v>
       </c>
@@ -5167,7 +5181,7 @@
       <c r="Q42" s="153"/>
     </row>
     <row r="43" spans="2:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="336"/>
+      <c r="B43" s="314"/>
       <c r="C43" s="204" t="s">
         <v>191</v>
       </c>
@@ -5188,7 +5202,7 @@
       <c r="P43" s="153"/>
       <c r="Q43" s="153"/>
     </row>
-    <row r="44" spans="2:17" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:17" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="147"/>
       <c r="C44" s="109"/>
       <c r="D44" s="148"/>
@@ -5204,14 +5218,14 @@
       <c r="P44" s="153"/>
       <c r="Q44" s="153"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B45" s="326" t="s">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B45" s="304" t="s">
         <v>213</v>
       </c>
       <c r="C45" s="154" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="327" t="s">
+      <c r="D45" s="305" t="s">
         <v>236</v>
       </c>
       <c r="E45" s="158"/>
@@ -5232,12 +5246,12 @@
       <c r="P45" s="90"/>
       <c r="Q45" s="90"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B46" s="326"/>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B46" s="304"/>
       <c r="C46" s="154" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="328"/>
+      <c r="D46" s="306"/>
       <c r="E46" s="158"/>
       <c r="F46" s="159"/>
       <c r="G46" s="159"/>
@@ -5255,12 +5269,12 @@
       <c r="P46" s="90"/>
       <c r="Q46" s="90"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B47" s="326"/>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B47" s="304"/>
       <c r="C47" s="154" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="328"/>
+      <c r="D47" s="306"/>
       <c r="E47" s="158"/>
       <c r="F47" s="159"/>
       <c r="G47" s="159"/>
@@ -5278,12 +5292,12 @@
       <c r="P47" s="90"/>
       <c r="Q47" s="90"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B48" s="326"/>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B48" s="304"/>
       <c r="C48" s="154" t="s">
         <v>155</v>
       </c>
-      <c r="D48" s="328"/>
+      <c r="D48" s="306"/>
       <c r="E48" s="158"/>
       <c r="F48" s="159"/>
       <c r="G48" s="159"/>
@@ -5301,12 +5315,12 @@
       <c r="P48" s="90"/>
       <c r="Q48" s="90"/>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B49" s="326"/>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B49" s="304"/>
       <c r="C49" s="154" t="s">
         <v>101</v>
       </c>
-      <c r="D49" s="328"/>
+      <c r="D49" s="306"/>
       <c r="E49" s="158"/>
       <c r="F49" s="159"/>
       <c r="G49" s="159"/>
@@ -5318,12 +5332,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B50" s="326"/>
+    <row r="50" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B50" s="304"/>
       <c r="C50" s="154" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="328"/>
+      <c r="D50" s="306"/>
       <c r="E50" s="158"/>
       <c r="F50" s="159"/>
       <c r="G50" s="159"/>
@@ -5335,10 +5349,10 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B51" s="326"/>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B51" s="304"/>
       <c r="C51" s="134"/>
-      <c r="D51" s="328"/>
+      <c r="D51" s="306"/>
       <c r="E51" s="135"/>
       <c r="F51" s="119"/>
       <c r="G51" s="119"/>
@@ -5346,12 +5360,12 @@
       <c r="I51" s="119"/>
       <c r="J51" s="123"/>
     </row>
-    <row r="52" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B52" s="326"/>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B52" s="304"/>
       <c r="C52" s="154" t="s">
         <v>128</v>
       </c>
-      <c r="D52" s="328"/>
+      <c r="D52" s="306"/>
       <c r="E52" s="158"/>
       <c r="F52" s="159"/>
       <c r="G52" s="159"/>
@@ -5362,12 +5376,12 @@
       </c>
       <c r="J52" s="164"/>
     </row>
-    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B53" s="326"/>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B53" s="304"/>
       <c r="C53" s="154" t="s">
         <v>166</v>
       </c>
-      <c r="D53" s="328"/>
+      <c r="D53" s="306"/>
       <c r="E53" s="158"/>
       <c r="F53" s="159"/>
       <c r="G53" s="159"/>
@@ -5378,12 +5392,12 @@
       </c>
       <c r="J53" s="164"/>
     </row>
-    <row r="54" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="326"/>
+    <row r="54" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="304"/>
       <c r="C54" s="154" t="s">
         <v>169</v>
       </c>
-      <c r="D54" s="328"/>
+      <c r="D54" s="306"/>
       <c r="E54" s="158"/>
       <c r="F54" s="159"/>
       <c r="G54" s="159"/>
@@ -5394,12 +5408,12 @@
       </c>
       <c r="J54" s="164"/>
     </row>
-    <row r="55" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="326"/>
+    <row r="55" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="304"/>
       <c r="C55" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="D55" s="328"/>
+      <c r="D55" s="306"/>
       <c r="E55" s="158"/>
       <c r="F55" s="159"/>
       <c r="G55" s="159"/>
@@ -5410,10 +5424,10 @@
       </c>
       <c r="J55" s="164"/>
     </row>
-    <row r="56" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="326"/>
+    <row r="56" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="304"/>
       <c r="C56" s="134"/>
-      <c r="D56" s="328"/>
+      <c r="D56" s="306"/>
       <c r="E56" s="135"/>
       <c r="F56" s="119"/>
       <c r="G56" s="119"/>
@@ -5422,12 +5436,12 @@
       <c r="J56" s="123"/>
       <c r="R56" s="81"/>
     </row>
-    <row r="57" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="326"/>
+    <row r="57" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="304"/>
       <c r="C57" s="154" t="s">
         <v>132</v>
       </c>
-      <c r="D57" s="328"/>
+      <c r="D57" s="306"/>
       <c r="E57" s="165"/>
       <c r="F57" s="166"/>
       <c r="G57" s="166"/>
@@ -5439,11 +5453,11 @@
       <c r="J57" s="164"/>
     </row>
     <row r="58" spans="2:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="326"/>
+      <c r="B58" s="304"/>
       <c r="C58" s="154" t="s">
         <v>167</v>
       </c>
-      <c r="D58" s="328"/>
+      <c r="D58" s="306"/>
       <c r="E58" s="165"/>
       <c r="F58" s="166"/>
       <c r="G58" s="166"/>
@@ -5454,12 +5468,12 @@
       </c>
       <c r="J58" s="164"/>
     </row>
-    <row r="59" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="326"/>
+    <row r="59" spans="2:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="304"/>
       <c r="C59" s="154" t="s">
         <v>136</v>
       </c>
-      <c r="D59" s="328"/>
+      <c r="D59" s="306"/>
       <c r="E59" s="165"/>
       <c r="F59" s="166"/>
       <c r="G59" s="166"/>
@@ -5470,10 +5484,10 @@
       </c>
       <c r="J59" s="164"/>
     </row>
-    <row r="60" spans="2:18" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="B60" s="326"/>
+    <row r="60" spans="2:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="B60" s="304"/>
       <c r="C60" s="134"/>
-      <c r="D60" s="328"/>
+      <c r="D60" s="306"/>
       <c r="E60" s="136"/>
       <c r="F60" s="121"/>
       <c r="G60" s="121"/>
@@ -5481,12 +5495,12 @@
       <c r="I60" s="121"/>
       <c r="J60" s="124"/>
     </row>
-    <row r="61" spans="2:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="326"/>
+    <row r="61" spans="2:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="304"/>
       <c r="C61" s="154" t="s">
         <v>168</v>
       </c>
-      <c r="D61" s="328"/>
+      <c r="D61" s="306"/>
       <c r="E61" s="165"/>
       <c r="F61" s="166"/>
       <c r="G61" s="166"/>
@@ -5499,12 +5513,12 @@
       <c r="P61" s="116"/>
       <c r="Q61" s="116"/>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B62" s="326"/>
+    <row r="62" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B62" s="304"/>
       <c r="C62" s="154" t="s">
         <v>137</v>
       </c>
-      <c r="D62" s="328"/>
+      <c r="D62" s="306"/>
       <c r="E62" s="165"/>
       <c r="F62" s="166"/>
       <c r="G62" s="166"/>
@@ -5516,12 +5530,12 @@
       <c r="P62" s="116"/>
       <c r="Q62" s="115"/>
     </row>
-    <row r="63" spans="2:18" ht="13.5" x14ac:dyDescent="0.35">
-      <c r="B63" s="326"/>
+    <row r="63" spans="2:18" ht="14.4" x14ac:dyDescent="0.35">
+      <c r="B63" s="304"/>
       <c r="C63" s="155" t="s">
         <v>129</v>
       </c>
-      <c r="D63" s="328"/>
+      <c r="D63" s="306"/>
       <c r="E63" s="169"/>
       <c r="F63" s="170"/>
       <c r="G63" s="170"/>
@@ -5534,12 +5548,12 @@
       <c r="P63" s="133"/>
       <c r="Q63" s="90"/>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B64" s="326"/>
+    <row r="64" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B64" s="304"/>
       <c r="C64" s="118" t="s">
         <v>215</v>
       </c>
-      <c r="D64" s="328"/>
+      <c r="D64" s="306"/>
       <c r="E64" s="119"/>
       <c r="F64" s="119"/>
       <c r="G64" s="119"/>
@@ -5551,12 +5565,12 @@
       <c r="P64" s="90"/>
       <c r="Q64" s="90"/>
     </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B65" s="326"/>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B65" s="304"/>
       <c r="C65" s="156" t="s">
         <v>100</v>
       </c>
-      <c r="D65" s="328"/>
+      <c r="D65" s="306"/>
       <c r="E65" s="166"/>
       <c r="F65" s="166"/>
       <c r="G65" s="166"/>
@@ -5568,12 +5582,12 @@
       <c r="P65" s="90"/>
       <c r="Q65" s="90"/>
     </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B66" s="326"/>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B66" s="304"/>
       <c r="C66" s="156" t="s">
         <v>164</v>
       </c>
-      <c r="D66" s="328"/>
+      <c r="D66" s="306"/>
       <c r="E66" s="166"/>
       <c r="F66" s="166"/>
       <c r="G66" s="166"/>
@@ -5583,12 +5597,12 @@
       </c>
       <c r="J66" s="164"/>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B67" s="326"/>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B67" s="304"/>
       <c r="C67" s="156" t="s">
         <v>273</v>
       </c>
-      <c r="D67" s="328"/>
+      <c r="D67" s="306"/>
       <c r="E67" s="166"/>
       <c r="F67" s="166"/>
       <c r="G67" s="166"/>
@@ -5598,12 +5612,12 @@
       </c>
       <c r="J67" s="164"/>
     </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B68" s="326"/>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B68" s="304"/>
       <c r="C68" s="156" t="s">
         <v>274</v>
       </c>
-      <c r="D68" s="328"/>
+      <c r="D68" s="306"/>
       <c r="E68" s="166"/>
       <c r="F68" s="166"/>
       <c r="G68" s="166"/>
@@ -5613,12 +5627,12 @@
       </c>
       <c r="J68" s="164"/>
     </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B69" s="326"/>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B69" s="304"/>
       <c r="C69" s="156" t="s">
         <v>99</v>
       </c>
-      <c r="D69" s="328"/>
+      <c r="D69" s="306"/>
       <c r="E69" s="166"/>
       <c r="F69" s="166"/>
       <c r="G69" s="166"/>
@@ -5628,12 +5642,12 @@
       </c>
       <c r="J69" s="164"/>
     </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B70" s="326"/>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B70" s="304"/>
       <c r="C70" s="156" t="s">
         <v>275</v>
       </c>
-      <c r="D70" s="328"/>
+      <c r="D70" s="306"/>
       <c r="E70" s="166"/>
       <c r="F70" s="166"/>
       <c r="G70" s="166"/>
@@ -5643,12 +5657,12 @@
       </c>
       <c r="J70" s="164"/>
     </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B71" s="326"/>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B71" s="304"/>
       <c r="C71" s="156" t="s">
         <v>282</v>
       </c>
-      <c r="D71" s="328"/>
+      <c r="D71" s="306"/>
       <c r="E71" s="166"/>
       <c r="F71" s="166"/>
       <c r="G71" s="166"/>
@@ -5658,12 +5672,12 @@
       </c>
       <c r="J71" s="164"/>
     </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B72" s="326"/>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B72" s="304"/>
       <c r="C72" s="156" t="s">
         <v>109</v>
       </c>
-      <c r="D72" s="328"/>
+      <c r="D72" s="306"/>
       <c r="E72" s="166"/>
       <c r="F72" s="166"/>
       <c r="G72" s="166"/>
@@ -5673,12 +5687,12 @@
       </c>
       <c r="J72" s="164"/>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B73" s="326"/>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B73" s="304"/>
       <c r="C73" s="156" t="s">
         <v>279</v>
       </c>
-      <c r="D73" s="328"/>
+      <c r="D73" s="306"/>
       <c r="E73" s="166"/>
       <c r="F73" s="166"/>
       <c r="G73" s="166"/>
@@ -5689,12 +5703,12 @@
       <c r="J73" s="164"/>
       <c r="P73" s="101"/>
     </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B74" s="326"/>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B74" s="304"/>
       <c r="C74" s="157" t="s">
         <v>280</v>
       </c>
-      <c r="D74" s="328"/>
+      <c r="D74" s="306"/>
       <c r="E74" s="166"/>
       <c r="F74" s="170"/>
       <c r="G74" s="170"/>
@@ -5705,12 +5719,12 @@
       <c r="J74" s="172"/>
       <c r="P74" s="101"/>
     </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B75" s="326"/>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B75" s="304"/>
       <c r="C75" s="157" t="s">
         <v>108</v>
       </c>
-      <c r="D75" s="328"/>
+      <c r="D75" s="306"/>
       <c r="E75" s="166"/>
       <c r="F75" s="170"/>
       <c r="G75" s="170"/>
@@ -5720,12 +5734,12 @@
       </c>
       <c r="J75" s="172"/>
     </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B76" s="326"/>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B76" s="304"/>
       <c r="C76" s="118" t="s">
         <v>206</v>
       </c>
-      <c r="D76" s="328"/>
+      <c r="D76" s="306"/>
       <c r="E76" s="119"/>
       <c r="F76" s="119"/>
       <c r="G76" s="119"/>
@@ -5733,13 +5747,13 @@
       <c r="I76" s="119"/>
       <c r="J76" s="120"/>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B77" s="326"/>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B77" s="304"/>
       <c r="C77" s="156">
         <f>I17</f>
         <v>0</v>
       </c>
-      <c r="D77" s="328"/>
+      <c r="D77" s="306"/>
       <c r="E77" s="166"/>
       <c r="F77" s="166"/>
       <c r="G77" s="166"/>
@@ -5751,13 +5765,13 @@
       <c r="J77" s="160"/>
       <c r="O77" s="90"/>
     </row>
-    <row r="78" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B78" s="326"/>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B78" s="304"/>
       <c r="C78" s="156">
         <f>I18</f>
         <v>0</v>
       </c>
-      <c r="D78" s="328"/>
+      <c r="D78" s="306"/>
       <c r="E78" s="166"/>
       <c r="F78" s="166"/>
       <c r="G78" s="166"/>
@@ -5769,13 +5783,13 @@
       <c r="J78" s="160"/>
       <c r="O78" s="90"/>
     </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B79" s="326"/>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B79" s="304"/>
       <c r="C79" s="156">
         <f>I19</f>
         <v>0</v>
       </c>
-      <c r="D79" s="328"/>
+      <c r="D79" s="306"/>
       <c r="E79" s="166"/>
       <c r="F79" s="166"/>
       <c r="G79" s="166"/>
@@ -5788,13 +5802,13 @@
       <c r="O79" s="90"/>
       <c r="P79" s="117"/>
     </row>
-    <row r="80" spans="2:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B80" s="326"/>
+    <row r="80" spans="2:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B80" s="304"/>
       <c r="C80" s="156">
         <f>I20</f>
         <v>0</v>
       </c>
-      <c r="D80" s="328"/>
+      <c r="D80" s="306"/>
       <c r="E80" s="166"/>
       <c r="F80" s="166"/>
       <c r="G80" s="166"/>
@@ -5809,12 +5823,12 @@
       <c r="S80" s="39"/>
       <c r="T80" s="39"/>
     </row>
-    <row r="81" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B81" s="326"/>
+    <row r="81" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B81" s="304"/>
       <c r="C81" s="118" t="s">
         <v>207</v>
       </c>
-      <c r="D81" s="328"/>
+      <c r="D81" s="306"/>
       <c r="E81" s="119"/>
       <c r="F81" s="119"/>
       <c r="G81" s="119"/>
@@ -5825,13 +5839,13 @@
       <c r="S81" s="38"/>
       <c r="T81" s="38"/>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B82" s="326"/>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B82" s="304"/>
       <c r="C82" s="156">
         <f>C77</f>
         <v>0</v>
       </c>
-      <c r="D82" s="328"/>
+      <c r="D82" s="306"/>
       <c r="E82" s="166"/>
       <c r="F82" s="166"/>
       <c r="G82" s="166"/>
@@ -5841,13 +5855,13 @@
       </c>
       <c r="J82" s="160"/>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B83" s="326"/>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B83" s="304"/>
       <c r="C83" s="156">
         <f>C78</f>
         <v>0</v>
       </c>
-      <c r="D83" s="328"/>
+      <c r="D83" s="306"/>
       <c r="E83" s="166"/>
       <c r="F83" s="166"/>
       <c r="G83" s="166"/>
@@ -5857,13 +5871,13 @@
       </c>
       <c r="J83" s="160"/>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B84" s="326"/>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B84" s="304"/>
       <c r="C84" s="156">
         <f>C79</f>
         <v>0</v>
       </c>
-      <c r="D84" s="328"/>
+      <c r="D84" s="306"/>
       <c r="E84" s="166"/>
       <c r="F84" s="166"/>
       <c r="G84" s="166"/>
@@ -5873,14 +5887,14 @@
       </c>
       <c r="J84" s="160"/>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="90"/>
-      <c r="B85" s="326"/>
+      <c r="B85" s="304"/>
       <c r="C85" s="156">
         <f>C80</f>
         <v>0</v>
       </c>
-      <c r="D85" s="328"/>
+      <c r="D85" s="306"/>
       <c r="E85" s="166"/>
       <c r="F85" s="166"/>
       <c r="G85" s="166"/>
@@ -5890,12 +5904,12 @@
       </c>
       <c r="J85" s="160"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B86" s="326"/>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B86" s="304"/>
       <c r="C86" s="118" t="s">
         <v>209</v>
       </c>
-      <c r="D86" s="328"/>
+      <c r="D86" s="306"/>
       <c r="E86" s="119"/>
       <c r="F86" s="119"/>
       <c r="G86" s="119"/>
@@ -5903,13 +5917,13 @@
       <c r="I86" s="119"/>
       <c r="J86" s="120"/>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B87" s="326"/>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B87" s="304"/>
       <c r="C87" s="156">
         <f>C82</f>
         <v>0</v>
       </c>
-      <c r="D87" s="328"/>
+      <c r="D87" s="306"/>
       <c r="E87" s="166"/>
       <c r="F87" s="166"/>
       <c r="G87" s="166"/>
@@ -5919,13 +5933,13 @@
       </c>
       <c r="J87" s="160"/>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B88" s="326"/>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B88" s="304"/>
       <c r="C88" s="156">
         <f>C83</f>
         <v>0</v>
       </c>
-      <c r="D88" s="328"/>
+      <c r="D88" s="306"/>
       <c r="E88" s="166"/>
       <c r="F88" s="166"/>
       <c r="G88" s="166"/>
@@ -5935,13 +5949,13 @@
       </c>
       <c r="J88" s="160"/>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B89" s="326"/>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B89" s="304"/>
       <c r="C89" s="156">
         <f>C84</f>
         <v>0</v>
       </c>
-      <c r="D89" s="328"/>
+      <c r="D89" s="306"/>
       <c r="E89" s="166"/>
       <c r="F89" s="166"/>
       <c r="G89" s="166"/>
@@ -5951,13 +5965,13 @@
       </c>
       <c r="J89" s="160"/>
     </row>
-    <row r="90" spans="1:20" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="326"/>
+    <row r="90" spans="1:20" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="304"/>
       <c r="C90" s="156">
         <f>C85</f>
         <v>0</v>
       </c>
-      <c r="D90" s="329"/>
+      <c r="D90" s="307"/>
       <c r="E90" s="166"/>
       <c r="F90" s="166"/>
       <c r="G90" s="166"/>
@@ -5967,7 +5981,7 @@
       </c>
       <c r="J90" s="160"/>
     </row>
-    <row r="94" spans="1:20" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:20" ht="23.4" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B94" s="254" t="s">
         <v>283</v>
       </c>
@@ -5976,7 +5990,7 @@
       <c r="E94"/>
       <c r="F94"/>
     </row>
-    <row r="95" spans="1:20" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:20" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="255" t="s">
         <v>268</v>
       </c>
@@ -5993,8 +6007,8 @@
         <v>272</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="310" t="s">
+    <row r="96" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="315" t="s">
         <v>100</v>
       </c>
       <c r="C96" s="259">
@@ -6002,98 +6016,98 @@
       </c>
       <c r="D96" s="260"/>
       <c r="E96" s="261"/>
-      <c r="F96" s="322">
+      <c r="F96" s="318">
         <f>SUM(E96:E105)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="311"/>
+    <row r="97" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="316"/>
       <c r="C97" s="262">
         <v>2</v>
       </c>
       <c r="D97" s="230"/>
       <c r="E97" s="263"/>
-      <c r="F97" s="317"/>
+      <c r="F97" s="319"/>
       <c r="G97" s="102"/>
       <c r="H97" s="88"/>
       <c r="I97" s="102"/>
       <c r="J97" s="88"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B98" s="311"/>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B98" s="316"/>
       <c r="C98" s="262">
         <v>3</v>
       </c>
       <c r="D98" s="230"/>
       <c r="E98" s="263"/>
-      <c r="F98" s="317"/>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B99" s="311"/>
+      <c r="F98" s="319"/>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B99" s="316"/>
       <c r="C99" s="262">
         <v>4</v>
       </c>
       <c r="D99" s="230"/>
       <c r="E99" s="263"/>
-      <c r="F99" s="317"/>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B100" s="311"/>
+      <c r="F99" s="319"/>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B100" s="316"/>
       <c r="C100" s="262">
         <v>5</v>
       </c>
       <c r="D100" s="230"/>
       <c r="E100" s="263"/>
-      <c r="F100" s="317"/>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B101" s="311"/>
+      <c r="F100" s="319"/>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B101" s="316"/>
       <c r="C101" s="262">
         <v>6</v>
       </c>
       <c r="D101" s="230"/>
       <c r="E101" s="263"/>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B102" s="311"/>
+      <c r="F101" s="319"/>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B102" s="316"/>
       <c r="C102" s="262">
         <v>7</v>
       </c>
       <c r="D102" s="230"/>
       <c r="E102" s="263"/>
-      <c r="F102" s="317"/>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B103" s="311"/>
+      <c r="F102" s="319"/>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B103" s="316"/>
       <c r="C103" s="262">
         <v>8</v>
       </c>
       <c r="D103" s="230"/>
       <c r="E103" s="263"/>
-      <c r="F103" s="317"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B104" s="311"/>
+      <c r="F103" s="319"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B104" s="316"/>
       <c r="C104" s="262">
         <v>9</v>
       </c>
       <c r="D104" s="230"/>
       <c r="E104" s="263"/>
-      <c r="F104" s="317"/>
-    </row>
-    <row r="105" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B105" s="312"/>
+      <c r="F104" s="319"/>
+    </row>
+    <row r="105" spans="2:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="317"/>
       <c r="C105" s="264">
         <v>10</v>
       </c>
       <c r="D105" s="265"/>
       <c r="E105" s="266"/>
-      <c r="F105" s="321"/>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B106" s="310" t="s">
+      <c r="F105" s="320"/>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B106" s="315" t="s">
         <v>164</v>
       </c>
       <c r="C106" s="259">
@@ -6101,94 +6115,94 @@
       </c>
       <c r="D106" s="260"/>
       <c r="E106" s="267"/>
-      <c r="F106" s="316">
+      <c r="F106" s="321">
         <f>SUM(E106:E115)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B107" s="311"/>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B107" s="316"/>
       <c r="C107" s="262">
         <v>2</v>
       </c>
       <c r="D107" s="230"/>
       <c r="E107" s="263"/>
-      <c r="F107" s="317"/>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B108" s="311"/>
+      <c r="F107" s="319"/>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B108" s="316"/>
       <c r="C108" s="262">
         <v>3</v>
       </c>
       <c r="D108" s="230"/>
       <c r="E108" s="263"/>
-      <c r="F108" s="317"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B109" s="311"/>
+      <c r="F108" s="319"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B109" s="316"/>
       <c r="C109" s="262">
         <v>4</v>
       </c>
       <c r="D109" s="230"/>
       <c r="E109" s="263"/>
-      <c r="F109" s="317"/>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B110" s="311"/>
+      <c r="F109" s="319"/>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B110" s="316"/>
       <c r="C110" s="262">
         <v>5</v>
       </c>
       <c r="D110" s="230"/>
       <c r="E110" s="263"/>
-      <c r="F110" s="317"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B111" s="311"/>
+      <c r="F110" s="319"/>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B111" s="316"/>
       <c r="C111" s="262">
         <v>6</v>
       </c>
       <c r="D111" s="230"/>
       <c r="E111" s="263"/>
-      <c r="F111" s="317"/>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B112" s="311"/>
+      <c r="F111" s="319"/>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B112" s="316"/>
       <c r="C112" s="262">
         <v>7</v>
       </c>
       <c r="D112" s="230"/>
       <c r="E112" s="263"/>
-      <c r="F112" s="317"/>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B113" s="311"/>
+      <c r="F112" s="319"/>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B113" s="316"/>
       <c r="C113" s="262">
         <v>8</v>
       </c>
       <c r="D113" s="230"/>
       <c r="E113" s="263"/>
-      <c r="F113" s="317"/>
-    </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B114" s="311"/>
+      <c r="F113" s="319"/>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B114" s="316"/>
       <c r="C114" s="262">
         <v>9</v>
       </c>
       <c r="D114" s="230"/>
       <c r="E114" s="263"/>
-      <c r="F114" s="317"/>
-    </row>
-    <row r="115" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="312"/>
+      <c r="F114" s="319"/>
+    </row>
+    <row r="115" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B115" s="317"/>
       <c r="C115" s="264">
         <v>10</v>
       </c>
       <c r="D115" s="265"/>
       <c r="E115" s="266"/>
-      <c r="F115" s="321"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B116" s="310" t="s">
+      <c r="F115" s="320"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="315" t="s">
         <v>273</v>
       </c>
       <c r="C116" s="259">
@@ -6196,94 +6210,94 @@
       </c>
       <c r="D116" s="260"/>
       <c r="E116" s="267"/>
-      <c r="F116" s="316">
+      <c r="F116" s="321">
         <f>SUM(E116:E125)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B117" s="311"/>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B117" s="316"/>
       <c r="C117" s="262">
         <v>2</v>
       </c>
       <c r="D117" s="230"/>
       <c r="E117" s="263"/>
-      <c r="F117" s="317"/>
-    </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B118" s="311"/>
+      <c r="F117" s="319"/>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B118" s="316"/>
       <c r="C118" s="262">
         <v>3</v>
       </c>
       <c r="D118" s="230"/>
       <c r="E118" s="263"/>
-      <c r="F118" s="317"/>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B119" s="311"/>
+      <c r="F118" s="319"/>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="316"/>
       <c r="C119" s="262">
         <v>4</v>
       </c>
       <c r="D119" s="230"/>
       <c r="E119" s="263"/>
-      <c r="F119" s="317"/>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B120" s="311"/>
+      <c r="F119" s="319"/>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B120" s="316"/>
       <c r="C120" s="262">
         <v>5</v>
       </c>
       <c r="D120" s="230"/>
       <c r="E120" s="263"/>
-      <c r="F120" s="317"/>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B121" s="311"/>
+      <c r="F120" s="319"/>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B121" s="316"/>
       <c r="C121" s="262">
         <v>6</v>
       </c>
       <c r="D121" s="230"/>
       <c r="E121" s="263"/>
-      <c r="F121" s="317"/>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B122" s="311"/>
+      <c r="F121" s="319"/>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B122" s="316"/>
       <c r="C122" s="262">
         <v>7</v>
       </c>
       <c r="D122" s="230"/>
       <c r="E122" s="263"/>
-      <c r="F122" s="317"/>
-    </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B123" s="311"/>
+      <c r="F122" s="319"/>
+    </row>
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B123" s="316"/>
       <c r="C123" s="262">
         <v>8</v>
       </c>
       <c r="D123" s="230"/>
       <c r="E123" s="263"/>
-      <c r="F123" s="317"/>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B124" s="311"/>
+      <c r="F123" s="319"/>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B124" s="316"/>
       <c r="C124" s="262">
         <v>9</v>
       </c>
       <c r="D124" s="230"/>
       <c r="E124" s="263"/>
-      <c r="F124" s="317"/>
-    </row>
-    <row r="125" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="312"/>
+      <c r="F124" s="319"/>
+    </row>
+    <row r="125" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="317"/>
       <c r="C125" s="264">
         <v>10</v>
       </c>
       <c r="D125" s="265"/>
       <c r="E125" s="266"/>
-      <c r="F125" s="321"/>
-    </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B126" s="310" t="s">
+      <c r="F125" s="320"/>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B126" s="315" t="s">
         <v>274</v>
       </c>
       <c r="C126" s="259">
@@ -6291,31 +6305,31 @@
       </c>
       <c r="D126" s="260"/>
       <c r="E126" s="267"/>
-      <c r="F126" s="316">
+      <c r="F126" s="321">
         <f>SUM(E126:E128)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B127" s="311"/>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B127" s="316"/>
       <c r="C127" s="262">
         <v>2</v>
       </c>
       <c r="D127" s="230"/>
       <c r="E127" s="263"/>
-      <c r="F127" s="317"/>
-    </row>
-    <row r="128" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B128" s="311"/>
+      <c r="F127" s="319"/>
+    </row>
+    <row r="128" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="316"/>
       <c r="C128" s="262">
         <v>3</v>
       </c>
       <c r="D128" s="230"/>
       <c r="E128" s="263"/>
-      <c r="F128" s="317"/>
-    </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B129" s="301" t="s">
+      <c r="F128" s="319"/>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B129" s="322" t="s">
         <v>275</v>
       </c>
       <c r="C129" s="268">
@@ -6323,85 +6337,85 @@
       </c>
       <c r="D129" s="269"/>
       <c r="E129" s="270"/>
-      <c r="F129" s="318">
+      <c r="F129" s="325">
         <f>SUM(E129:E137)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B130" s="302"/>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B130" s="323"/>
       <c r="C130" s="271">
         <v>2</v>
       </c>
       <c r="D130" s="272"/>
       <c r="E130" s="273"/>
-      <c r="F130" s="319"/>
-    </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B131" s="302"/>
+      <c r="F130" s="326"/>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B131" s="323"/>
       <c r="C131" s="271">
         <v>3</v>
       </c>
       <c r="D131" s="272"/>
       <c r="E131" s="273"/>
-      <c r="F131" s="319"/>
-    </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B132" s="302"/>
+      <c r="F131" s="326"/>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B132" s="323"/>
       <c r="C132" s="271">
         <v>4</v>
       </c>
       <c r="D132" s="272"/>
       <c r="E132" s="273"/>
-      <c r="F132" s="319"/>
-    </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B133" s="302"/>
+      <c r="F132" s="326"/>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B133" s="323"/>
       <c r="C133" s="271">
         <v>5</v>
       </c>
       <c r="D133" s="272"/>
       <c r="E133" s="273"/>
-      <c r="F133" s="319"/>
-    </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B134" s="302"/>
+      <c r="F133" s="326"/>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B134" s="323"/>
       <c r="C134" s="271">
         <v>6</v>
       </c>
       <c r="D134" s="272"/>
       <c r="E134" s="273"/>
-      <c r="F134" s="319"/>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B135" s="302"/>
+      <c r="F134" s="326"/>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B135" s="323"/>
       <c r="C135" s="271">
         <v>7</v>
       </c>
       <c r="D135" s="272"/>
       <c r="E135" s="273"/>
-      <c r="F135" s="319"/>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B136" s="302"/>
+      <c r="F135" s="326"/>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B136" s="323"/>
       <c r="C136" s="274">
         <v>8</v>
       </c>
       <c r="D136" s="275"/>
       <c r="E136" s="276"/>
-      <c r="F136" s="319"/>
-    </row>
-    <row r="137" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B137" s="303"/>
+      <c r="F136" s="326"/>
+    </row>
+    <row r="137" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B137" s="324"/>
       <c r="C137" s="277">
         <v>9</v>
       </c>
       <c r="D137" s="278"/>
       <c r="E137" s="279"/>
-      <c r="F137" s="320"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B138" s="310" t="s">
+      <c r="F137" s="327"/>
+    </row>
+    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B138" s="315" t="s">
         <v>276</v>
       </c>
       <c r="C138" s="280">
@@ -6409,94 +6423,94 @@
       </c>
       <c r="D138" s="281"/>
       <c r="E138" s="282"/>
-      <c r="F138" s="316">
+      <c r="F138" s="321">
         <f>SUM(E138:E147)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B139" s="311"/>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B139" s="316"/>
       <c r="C139" s="262">
         <v>2</v>
       </c>
       <c r="D139" s="230"/>
       <c r="E139" s="263"/>
-      <c r="F139" s="317"/>
-    </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B140" s="311"/>
+      <c r="F139" s="319"/>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B140" s="316"/>
       <c r="C140" s="262">
         <v>3</v>
       </c>
       <c r="D140" s="230"/>
       <c r="E140" s="263"/>
-      <c r="F140" s="317"/>
-    </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B141" s="311"/>
+      <c r="F140" s="319"/>
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B141" s="316"/>
       <c r="C141" s="262">
         <v>4</v>
       </c>
       <c r="D141" s="230"/>
       <c r="E141" s="263"/>
-      <c r="F141" s="317"/>
-    </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B142" s="311"/>
+      <c r="F141" s="319"/>
+    </row>
+    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B142" s="316"/>
       <c r="C142" s="262">
         <v>5</v>
       </c>
       <c r="D142" s="230"/>
       <c r="E142" s="263"/>
-      <c r="F142" s="317"/>
-    </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B143" s="311"/>
+      <c r="F142" s="319"/>
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B143" s="316"/>
       <c r="C143" s="262">
         <v>6</v>
       </c>
       <c r="D143" s="230"/>
       <c r="E143" s="263"/>
-      <c r="F143" s="317"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B144" s="311"/>
+      <c r="F143" s="319"/>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B144" s="316"/>
       <c r="C144" s="262">
         <v>7</v>
       </c>
       <c r="D144" s="230"/>
       <c r="E144" s="263"/>
-      <c r="F144" s="317"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B145" s="311"/>
+      <c r="F144" s="319"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B145" s="316"/>
       <c r="C145" s="262">
         <v>8</v>
       </c>
       <c r="D145" s="230"/>
       <c r="E145" s="263"/>
-      <c r="F145" s="317"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B146" s="311"/>
+      <c r="F145" s="319"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B146" s="316"/>
       <c r="C146" s="262">
         <v>9</v>
       </c>
       <c r="D146" s="230"/>
       <c r="E146" s="263"/>
-      <c r="F146" s="317"/>
-    </row>
-    <row r="147" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="312"/>
+      <c r="F146" s="319"/>
+    </row>
+    <row r="147" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B147" s="317"/>
       <c r="C147" s="283">
         <v>10</v>
       </c>
       <c r="D147" s="231"/>
       <c r="E147" s="284"/>
-      <c r="F147" s="321"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B148" s="310" t="s">
+      <c r="F147" s="320"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B148" s="315" t="s">
         <v>277</v>
       </c>
       <c r="C148" s="285">
@@ -6504,94 +6518,94 @@
       </c>
       <c r="D148" s="260"/>
       <c r="E148" s="286"/>
-      <c r="F148" s="313">
+      <c r="F148" s="328">
         <f>SUM(E148:E157)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B149" s="311"/>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B149" s="316"/>
       <c r="C149" s="287">
         <v>2</v>
       </c>
       <c r="D149" s="230"/>
       <c r="E149" s="288"/>
-      <c r="F149" s="314"/>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B150" s="311"/>
+      <c r="F149" s="329"/>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B150" s="316"/>
       <c r="C150" s="287">
         <v>3</v>
       </c>
       <c r="D150" s="230"/>
       <c r="E150" s="288"/>
-      <c r="F150" s="314"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B151" s="311"/>
+      <c r="F150" s="329"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B151" s="316"/>
       <c r="C151" s="287">
         <v>4</v>
       </c>
       <c r="D151" s="230"/>
       <c r="E151" s="288"/>
-      <c r="F151" s="314"/>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B152" s="311"/>
+      <c r="F151" s="329"/>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B152" s="316"/>
       <c r="C152" s="287">
         <v>5</v>
       </c>
       <c r="D152" s="230"/>
       <c r="E152" s="288"/>
-      <c r="F152" s="314"/>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B153" s="311"/>
+      <c r="F152" s="329"/>
+    </row>
+    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B153" s="316"/>
       <c r="C153" s="287">
         <v>6</v>
       </c>
       <c r="D153" s="230"/>
       <c r="E153" s="288"/>
-      <c r="F153" s="314"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B154" s="311"/>
+      <c r="F153" s="329"/>
+    </row>
+    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B154" s="316"/>
       <c r="C154" s="287">
         <v>7</v>
       </c>
       <c r="D154" s="230"/>
       <c r="E154" s="288"/>
-      <c r="F154" s="314"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B155" s="311"/>
+      <c r="F154" s="329"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B155" s="316"/>
       <c r="C155" s="287">
         <v>8</v>
       </c>
       <c r="D155" s="230"/>
       <c r="E155" s="288"/>
-      <c r="F155" s="314"/>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B156" s="311"/>
+      <c r="F155" s="329"/>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B156" s="316"/>
       <c r="C156" s="287">
         <v>9</v>
       </c>
       <c r="D156" s="230"/>
       <c r="E156" s="288"/>
-      <c r="F156" s="314"/>
-    </row>
-    <row r="157" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="312"/>
+      <c r="F156" s="329"/>
+    </row>
+    <row r="157" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B157" s="317"/>
       <c r="C157" s="289">
         <v>10</v>
       </c>
       <c r="D157" s="265"/>
       <c r="E157" s="290"/>
-      <c r="F157" s="315"/>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B158" s="311" t="s">
+      <c r="F157" s="330"/>
+    </row>
+    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B158" s="316" t="s">
         <v>278</v>
       </c>
       <c r="C158" s="285">
@@ -6599,94 +6613,94 @@
       </c>
       <c r="D158" s="260"/>
       <c r="E158" s="267"/>
-      <c r="F158" s="304">
+      <c r="F158" s="331">
         <f>SUM(E158:E167)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B159" s="311"/>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B159" s="316"/>
       <c r="C159" s="287">
         <v>2</v>
       </c>
       <c r="D159" s="230"/>
       <c r="E159" s="263"/>
-      <c r="F159" s="305"/>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B160" s="311"/>
+      <c r="F159" s="332"/>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B160" s="316"/>
       <c r="C160" s="287">
         <v>3</v>
       </c>
       <c r="D160" s="230"/>
       <c r="E160" s="263"/>
-      <c r="F160" s="305"/>
-    </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B161" s="311"/>
+      <c r="F160" s="332"/>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B161" s="316"/>
       <c r="C161" s="287">
         <v>4</v>
       </c>
       <c r="D161" s="230"/>
       <c r="E161" s="263"/>
-      <c r="F161" s="305"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B162" s="311"/>
+      <c r="F161" s="332"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B162" s="316"/>
       <c r="C162" s="287">
         <v>5</v>
       </c>
       <c r="D162" s="230"/>
       <c r="E162" s="263"/>
-      <c r="F162" s="305"/>
-    </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B163" s="311"/>
+      <c r="F162" s="332"/>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B163" s="316"/>
       <c r="C163" s="287">
         <v>6</v>
       </c>
       <c r="D163" s="230"/>
       <c r="E163" s="263"/>
-      <c r="F163" s="305"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B164" s="311"/>
+      <c r="F163" s="332"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B164" s="316"/>
       <c r="C164" s="287">
         <v>7</v>
       </c>
       <c r="D164" s="230"/>
       <c r="E164" s="263"/>
-      <c r="F164" s="305"/>
-    </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B165" s="311"/>
+      <c r="F164" s="332"/>
+    </row>
+    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B165" s="316"/>
       <c r="C165" s="287">
         <v>8</v>
       </c>
       <c r="D165" s="230"/>
       <c r="E165" s="263"/>
-      <c r="F165" s="305"/>
-    </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B166" s="311"/>
+      <c r="F165" s="332"/>
+    </row>
+    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B166" s="316"/>
       <c r="C166" s="287">
         <v>9</v>
       </c>
       <c r="D166" s="230"/>
       <c r="E166" s="263"/>
-      <c r="F166" s="305"/>
-    </row>
-    <row r="167" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B167" s="312"/>
+      <c r="F166" s="332"/>
+    </row>
+    <row r="167" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="317"/>
       <c r="C167" s="289">
         <v>10</v>
       </c>
       <c r="D167" s="265"/>
       <c r="E167" s="266"/>
-      <c r="F167" s="306"/>
-    </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B168" s="310" t="s">
+      <c r="F167" s="333"/>
+    </row>
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B168" s="315" t="s">
         <v>279</v>
       </c>
       <c r="C168" s="280">
@@ -6694,85 +6708,85 @@
       </c>
       <c r="D168" s="281"/>
       <c r="E168" s="282"/>
-      <c r="F168" s="304">
+      <c r="F168" s="331">
         <f>SUM(E168:E176)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B169" s="311"/>
+    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B169" s="316"/>
       <c r="C169" s="262">
         <v>2</v>
       </c>
       <c r="D169" s="230"/>
       <c r="E169" s="263"/>
-      <c r="F169" s="305"/>
-    </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B170" s="311"/>
+      <c r="F169" s="332"/>
+    </row>
+    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B170" s="316"/>
       <c r="C170" s="262">
         <v>3</v>
       </c>
       <c r="D170" s="230"/>
       <c r="E170" s="263"/>
-      <c r="F170" s="305"/>
-    </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B171" s="311"/>
+      <c r="F170" s="332"/>
+    </row>
+    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B171" s="316"/>
       <c r="C171" s="262">
         <v>4</v>
       </c>
       <c r="D171" s="230"/>
       <c r="E171" s="263"/>
-      <c r="F171" s="305"/>
-    </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B172" s="311"/>
+      <c r="F171" s="332"/>
+    </row>
+    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B172" s="316"/>
       <c r="C172" s="262">
         <v>5</v>
       </c>
       <c r="D172" s="230"/>
       <c r="E172" s="263"/>
-      <c r="F172" s="305"/>
-    </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B173" s="311"/>
+      <c r="F172" s="332"/>
+    </row>
+    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B173" s="316"/>
       <c r="C173" s="262">
         <v>6</v>
       </c>
       <c r="D173" s="230"/>
       <c r="E173" s="263"/>
-      <c r="F173" s="305"/>
-    </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B174" s="311"/>
+      <c r="F173" s="332"/>
+    </row>
+    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B174" s="316"/>
       <c r="C174" s="262">
         <v>7</v>
       </c>
       <c r="D174" s="230"/>
       <c r="E174" s="263"/>
-      <c r="F174" s="305"/>
-    </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B175" s="311"/>
+      <c r="F174" s="332"/>
+    </row>
+    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B175" s="316"/>
       <c r="C175" s="262">
         <v>8</v>
       </c>
       <c r="D175" s="230"/>
       <c r="E175" s="263"/>
-      <c r="F175" s="305"/>
-    </row>
-    <row r="176" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B176" s="311"/>
+      <c r="F175" s="332"/>
+    </row>
+    <row r="176" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B176" s="316"/>
       <c r="C176" s="283">
         <v>9</v>
       </c>
       <c r="D176" s="231"/>
       <c r="E176" s="284"/>
-      <c r="F176" s="306"/>
-    </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B177" s="301" t="s">
+      <c r="F176" s="333"/>
+    </row>
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B177" s="322" t="s">
         <v>108</v>
       </c>
       <c r="C177" s="268">
@@ -6780,94 +6794,94 @@
       </c>
       <c r="D177" s="269"/>
       <c r="E177" s="291"/>
-      <c r="F177" s="304">
+      <c r="F177" s="331">
         <f>SUM(E177:E186)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B178" s="302"/>
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B178" s="323"/>
       <c r="C178" s="274">
         <v>2</v>
       </c>
       <c r="D178" s="275"/>
       <c r="E178" s="292"/>
-      <c r="F178" s="305"/>
-    </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B179" s="302"/>
+      <c r="F178" s="332"/>
+    </row>
+    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B179" s="323"/>
       <c r="C179" s="274">
         <v>3</v>
       </c>
       <c r="D179" s="275"/>
       <c r="E179" s="292"/>
-      <c r="F179" s="305"/>
-    </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B180" s="302"/>
+      <c r="F179" s="332"/>
+    </row>
+    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B180" s="323"/>
       <c r="C180" s="274">
         <v>4</v>
       </c>
       <c r="D180" s="275"/>
       <c r="E180" s="292"/>
-      <c r="F180" s="305"/>
-    </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B181" s="302"/>
+      <c r="F180" s="332"/>
+    </row>
+    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B181" s="323"/>
       <c r="C181" s="274">
         <v>5</v>
       </c>
       <c r="D181" s="275"/>
       <c r="E181" s="292"/>
-      <c r="F181" s="305"/>
-    </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B182" s="302"/>
+      <c r="F181" s="332"/>
+    </row>
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B182" s="323"/>
       <c r="C182" s="274">
         <v>6</v>
       </c>
       <c r="D182" s="275"/>
       <c r="E182" s="292"/>
-      <c r="F182" s="305"/>
-    </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B183" s="302"/>
+      <c r="F182" s="332"/>
+    </row>
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B183" s="323"/>
       <c r="C183" s="274">
         <v>7</v>
       </c>
       <c r="D183" s="275"/>
       <c r="E183" s="292"/>
-      <c r="F183" s="305"/>
-    </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B184" s="302"/>
+      <c r="F183" s="332"/>
+    </row>
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B184" s="323"/>
       <c r="C184" s="274">
         <v>8</v>
       </c>
       <c r="D184" s="275"/>
       <c r="E184" s="292"/>
-      <c r="F184" s="305"/>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B185" s="302"/>
+      <c r="F184" s="332"/>
+    </row>
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B185" s="323"/>
       <c r="C185" s="274">
         <v>9</v>
       </c>
       <c r="D185" s="275"/>
       <c r="E185" s="292"/>
-      <c r="F185" s="305"/>
-    </row>
-    <row r="186" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B186" s="303"/>
+      <c r="F185" s="332"/>
+    </row>
+    <row r="186" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B186" s="324"/>
       <c r="C186" s="277">
         <v>10</v>
       </c>
       <c r="D186" s="278"/>
       <c r="E186" s="293"/>
-      <c r="F186" s="306"/>
-    </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B187" s="301" t="s">
+      <c r="F186" s="333"/>
+    </row>
+    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B187" s="322" t="s">
         <v>280</v>
       </c>
       <c r="C187" s="268">
@@ -6875,99 +6889,99 @@
       </c>
       <c r="D187" s="269"/>
       <c r="E187" s="291"/>
-      <c r="F187" s="304">
+      <c r="F187" s="331">
         <f>SUM(E187:E196)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B188" s="302"/>
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B188" s="323"/>
       <c r="C188" s="274">
         <v>2</v>
       </c>
       <c r="D188" s="275"/>
       <c r="E188" s="292"/>
-      <c r="F188" s="305"/>
-    </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B189" s="302"/>
+      <c r="F188" s="332"/>
+    </row>
+    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B189" s="323"/>
       <c r="C189" s="274">
         <v>3</v>
       </c>
       <c r="D189" s="275"/>
       <c r="E189" s="292"/>
-      <c r="F189" s="305"/>
-    </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B190" s="302"/>
+      <c r="F189" s="332"/>
+    </row>
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B190" s="323"/>
       <c r="C190" s="274">
         <v>4</v>
       </c>
       <c r="D190" s="275"/>
       <c r="E190" s="292"/>
-      <c r="F190" s="305"/>
-    </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B191" s="302"/>
+      <c r="F190" s="332"/>
+    </row>
+    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B191" s="323"/>
       <c r="C191" s="274">
         <v>5</v>
       </c>
       <c r="D191" s="275"/>
       <c r="E191" s="292"/>
-      <c r="F191" s="305"/>
-    </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B192" s="302"/>
+      <c r="F191" s="332"/>
+    </row>
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B192" s="323"/>
       <c r="C192" s="274">
         <v>6</v>
       </c>
       <c r="D192" s="275"/>
       <c r="E192" s="292"/>
-      <c r="F192" s="305"/>
-    </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B193" s="302"/>
+      <c r="F192" s="332"/>
+    </row>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B193" s="323"/>
       <c r="C193" s="274">
         <v>7</v>
       </c>
       <c r="D193" s="275"/>
       <c r="E193" s="292"/>
-      <c r="F193" s="305"/>
-    </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B194" s="302"/>
+      <c r="F193" s="332"/>
+    </row>
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B194" s="323"/>
       <c r="C194" s="274">
         <v>8</v>
       </c>
       <c r="D194" s="275"/>
       <c r="E194" s="292"/>
-      <c r="F194" s="305"/>
-    </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B195" s="302"/>
+      <c r="F194" s="332"/>
+    </row>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B195" s="323"/>
       <c r="C195" s="274">
         <v>9</v>
       </c>
       <c r="D195" s="275"/>
       <c r="E195" s="292"/>
-      <c r="F195" s="305"/>
-    </row>
-    <row r="196" spans="2:6" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B196" s="303"/>
+      <c r="F195" s="332"/>
+    </row>
+    <row r="196" spans="2:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B196" s="324"/>
       <c r="C196" s="277">
         <v>10</v>
       </c>
       <c r="D196" s="278"/>
       <c r="E196" s="293"/>
-      <c r="F196" s="306"/>
-    </row>
-    <row r="197" spans="2:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B197" s="307" t="s">
+      <c r="F196" s="333"/>
+    </row>
+    <row r="197" spans="2:6" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B197" s="334" t="s">
         <v>281</v>
       </c>
-      <c r="C197" s="308"/>
-      <c r="D197" s="308"/>
-      <c r="E197" s="309"/>
+      <c r="C197" s="335"/>
+      <c r="D197" s="335"/>
+      <c r="E197" s="336"/>
       <c r="F197" s="294">
         <f>SUM(F96:F196)</f>
         <v>0</v>
@@ -6975,6 +6989,29 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B177:B186"/>
+    <mergeCell ref="F177:F186"/>
+    <mergeCell ref="B187:B196"/>
+    <mergeCell ref="F187:F196"/>
+    <mergeCell ref="B197:E197"/>
+    <mergeCell ref="B148:B157"/>
+    <mergeCell ref="F148:F157"/>
+    <mergeCell ref="B158:B167"/>
+    <mergeCell ref="F158:F167"/>
+    <mergeCell ref="B168:B176"/>
+    <mergeCell ref="F168:F176"/>
+    <mergeCell ref="B126:B128"/>
+    <mergeCell ref="F126:F128"/>
+    <mergeCell ref="B129:B137"/>
+    <mergeCell ref="F129:F137"/>
+    <mergeCell ref="B138:B147"/>
+    <mergeCell ref="F138:F147"/>
+    <mergeCell ref="B96:B105"/>
+    <mergeCell ref="F96:F105"/>
+    <mergeCell ref="B106:B115"/>
+    <mergeCell ref="F106:F115"/>
+    <mergeCell ref="B116:B125"/>
+    <mergeCell ref="F116:F125"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="B45:B90"/>
@@ -6983,29 +7020,6 @@
     <mergeCell ref="B11:B15"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="B22:B43"/>
-    <mergeCell ref="B96:B105"/>
-    <mergeCell ref="F96:F105"/>
-    <mergeCell ref="B106:B115"/>
-    <mergeCell ref="F106:F115"/>
-    <mergeCell ref="B116:B125"/>
-    <mergeCell ref="F116:F125"/>
-    <mergeCell ref="B126:B128"/>
-    <mergeCell ref="F126:F128"/>
-    <mergeCell ref="B129:B137"/>
-    <mergeCell ref="F129:F137"/>
-    <mergeCell ref="B138:B147"/>
-    <mergeCell ref="F138:F147"/>
-    <mergeCell ref="B148:B157"/>
-    <mergeCell ref="F148:F157"/>
-    <mergeCell ref="B158:B167"/>
-    <mergeCell ref="F158:F167"/>
-    <mergeCell ref="B168:B176"/>
-    <mergeCell ref="F168:F176"/>
-    <mergeCell ref="B177:B186"/>
-    <mergeCell ref="F177:F186"/>
-    <mergeCell ref="B187:B196"/>
-    <mergeCell ref="F187:F196"/>
-    <mergeCell ref="B197:E197"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -7016,34 +7030,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V110"/>
-  <sheetFormatPr defaultColWidth="21.81640625" defaultRowHeight="25.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="55.26953125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.81640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.453125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.26953125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="55.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.21875" style="2" customWidth="1"/>
     <col min="6" max="6" width="31" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="21.81640625" style="2"/>
+    <col min="7" max="16384" width="21.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="345"/>
-      <c r="B1" s="345"/>
-      <c r="C1" s="345"/>
-      <c r="D1" s="345"/>
-      <c r="E1" s="345"/>
-      <c r="F1" s="345"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="345"/>
-      <c r="B2" s="345"/>
-      <c r="C2" s="345"/>
-      <c r="D2" s="345"/>
-      <c r="E2" s="345"/>
-      <c r="F2" s="345"/>
-    </row>
-    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A1" s="339"/>
+      <c r="B1" s="339"/>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+      <c r="F1" s="339"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A2" s="339"/>
+      <c r="B2" s="339"/>
+      <c r="C2" s="339"/>
+      <c r="D2" s="339"/>
+      <c r="E2" s="339"/>
+      <c r="F2" s="339"/>
+    </row>
+    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A3" s="346" t="s">
         <v>200</v>
       </c>
@@ -7052,26 +7066,26 @@
       <c r="D3" s="346"/>
       <c r="E3" s="346"/>
       <c r="F3" s="346"/>
-      <c r="M3" s="350"/>
-      <c r="N3" s="350"/>
-      <c r="O3" s="350"/>
-    </row>
-    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="1">
-      <c r="A4" s="341" t="s">
+      <c r="M3" s="337"/>
+      <c r="N3" s="337"/>
+      <c r="O3" s="337"/>
+    </row>
+    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A4" s="338" t="s">
         <v>201</v>
       </c>
-      <c r="B4" s="341"/>
-      <c r="C4" s="341"/>
-      <c r="D4" s="341"/>
-      <c r="E4" s="341"/>
-      <c r="F4" s="341"/>
+      <c r="B4" s="338"/>
+      <c r="C4" s="338"/>
+      <c r="D4" s="338"/>
+      <c r="E4" s="338"/>
+      <c r="F4" s="338"/>
       <c r="H4" s="132"/>
     </row>
-    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="347" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="342" t="s">
+      <c r="B5" s="343" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="89" t="str">
@@ -7091,9 +7105,9 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="348"/>
-      <c r="B6" s="343"/>
+      <c r="B6" s="344"/>
       <c r="C6" s="125">
         <f>Assumptions.1!I17</f>
         <v>0</v>
@@ -7112,31 +7126,31 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="349"/>
-      <c r="B7" s="344"/>
+      <c r="B7" s="345"/>
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
       <c r="E7" s="57"/>
       <c r="F7" s="57"/>
     </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="26.4" thickTop="1" x14ac:dyDescent="0.5">
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:15" s="3" customFormat="1" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="340"/>
-      <c r="E9" s="340"/>
-      <c r="F9" s="340"/>
-    </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" s="350"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
+    </row>
+    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A10" s="5"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
         <v>170</v>
       </c>
@@ -7158,7 +7172,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="6"/>
@@ -7166,7 +7180,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C13" s="7">
         <f>SUM(C11:C12)</f>
         <v>0</v>
@@ -7184,15 +7198,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
@@ -7214,7 +7228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
         <v>93</v>
       </c>
@@ -7238,7 +7252,7 @@
       <c r="L18"/>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2" t="s">
         <v>2</v>
       </c>
@@ -7260,7 +7274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="3" t="s">
         <v>67</v>
       </c>
@@ -7281,12 +7295,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5"/>
       <c r="C21" s="3"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="5" t="s">
         <v>171</v>
       </c>
@@ -7312,10 +7326,10 @@
       <c r="K22" s="82"/>
       <c r="L22" s="82"/>
     </row>
-    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="2" t="s">
         <v>159</v>
       </c>
@@ -7337,7 +7351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -7345,7 +7359,7 @@
       <c r="F25" s="7"/>
       <c r="V25"/>
     </row>
-    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="2" t="s">
         <v>160</v>
       </c>
@@ -7372,7 +7386,7 @@
       <c r="K26" s="86"/>
       <c r="L26" s="86"/>
     </row>
-    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B27" s="11"/>
       <c r="H27" s="83"/>
       <c r="I27" s="83"/>
@@ -7380,7 +7394,7 @@
       <c r="K27" s="83"/>
       <c r="L27" s="83"/>
     </row>
-    <row r="28" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="5" t="s">
         <v>172</v>
       </c>
@@ -7407,7 +7421,7 @@
       <c r="K28" s="83"/>
       <c r="L28" s="83"/>
     </row>
-    <row r="29" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="3"/>
       <c r="B29" s="11"/>
       <c r="H29" s="86"/>
@@ -7416,7 +7430,7 @@
       <c r="K29" s="86"/>
       <c r="L29" s="86"/>
     </row>
-    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="2" t="s">
         <v>173</v>
       </c>
@@ -7443,7 +7457,7 @@
       <c r="K30" s="83"/>
       <c r="L30" s="83"/>
     </row>
-    <row r="31" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B31" s="11"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -7455,7 +7469,7 @@
       <c r="K31" s="83"/>
       <c r="L31" s="83"/>
     </row>
-    <row r="32" spans="1:22" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:22" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="5" t="s">
         <v>162</v>
       </c>
@@ -7481,7 +7495,7 @@
       <c r="K32" s="84"/>
       <c r="L32" s="84"/>
     </row>
-    <row r="33" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="3"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -7492,7 +7506,7 @@
       <c r="K33" s="83"/>
       <c r="L33" s="83"/>
     </row>
-    <row r="34" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="2" t="s">
         <v>161</v>
       </c>
@@ -7519,14 +7533,14 @@
       <c r="K34" s="83"/>
       <c r="L34" s="83"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.5">
       <c r="H35" s="83"/>
       <c r="I35" s="83"/>
       <c r="J35" s="83"/>
       <c r="K35" s="83"/>
       <c r="L35" s="83"/>
     </row>
-    <row r="36" spans="1:18" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="8" t="s">
         <v>163</v>
       </c>
@@ -7553,50 +7567,50 @@
       <c r="K36" s="85"/>
       <c r="L36" s="85"/>
     </row>
-    <row r="37" spans="1:18" s="3" customFormat="1" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:18" s="3" customFormat="1" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
     </row>
-    <row r="38" spans="1:18" ht="26" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:18" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
-      <c r="C38" s="337" t="s">
+      <c r="C38" s="340" t="s">
         <v>158</v>
       </c>
-      <c r="D38" s="338"/>
-      <c r="E38" s="338"/>
-      <c r="F38" s="339"/>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="D38" s="341"/>
+      <c r="E38" s="341"/>
+      <c r="F38" s="342"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.5">
       <c r="C39" s="126"/>
       <c r="D39" s="126"/>
       <c r="E39" s="126"/>
       <c r="F39" s="126"/>
     </row>
-    <row r="40" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="345"/>
-      <c r="B40" s="345"/>
-      <c r="C40" s="345"/>
-      <c r="D40" s="345"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
-    </row>
-    <row r="41" spans="1:18" ht="48.75" customHeight="1" x14ac:dyDescent="1">
-      <c r="A41" s="341" t="s">
+    <row r="40" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="339"/>
+      <c r="B40" s="339"/>
+      <c r="C40" s="339"/>
+      <c r="D40" s="339"/>
+      <c r="E40" s="339"/>
+      <c r="F40" s="339"/>
+    </row>
+    <row r="41" spans="1:18" ht="48.75" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="A41" s="338" t="s">
         <v>202</v>
       </c>
-      <c r="B41" s="341"/>
-      <c r="C41" s="341"/>
-      <c r="D41" s="341"/>
-      <c r="E41" s="341"/>
-      <c r="F41" s="341"/>
+      <c r="B41" s="338"/>
+      <c r="C41" s="338"/>
+      <c r="D41" s="338"/>
+      <c r="E41" s="338"/>
+      <c r="F41" s="338"/>
       <c r="H41" s="132"/>
     </row>
-    <row r="42" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="342" t="s">
+    <row r="42" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A42" s="343" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="342" t="s">
+      <c r="B42" s="343" t="s">
         <v>37</v>
       </c>
       <c r="C42" s="89" t="str">
@@ -7616,9 +7630,9 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="343"/>
-      <c r="B43" s="343"/>
+    <row r="43" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A43" s="344"/>
+      <c r="B43" s="344"/>
       <c r="C43" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -7636,26 +7650,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="344"/>
-      <c r="B44" s="344"/>
+    <row r="44" spans="1:18" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="345"/>
+      <c r="B44" s="345"/>
       <c r="C44" s="57"/>
       <c r="D44" s="57"/>
       <c r="E44" s="57"/>
       <c r="F44" s="57"/>
       <c r="R44"/>
     </row>
-    <row r="45" spans="1:18" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:18" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="A45" s="44" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="31" x14ac:dyDescent="0.7">
+    <row r="46" spans="1:18" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="D46" s="145"/>
       <c r="E46" s="145"/>
       <c r="F46" s="145"/>
     </row>
-    <row r="47" spans="1:18" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="2" t="s">
         <v>76</v>
       </c>
@@ -7679,20 +7693,20 @@
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
     </row>
-    <row r="48" spans="1:18" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:18" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="56" t="s">
         <v>77</v>
       </c>
       <c r="B48" s="10"/>
       <c r="J48"/>
     </row>
-    <row r="49" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B49" s="10"/>
     </row>
-    <row r="50" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="2" t="s">
         <v>131</v>
       </c>
@@ -7714,21 +7728,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B51" s="10"/>
       <c r="C51" s="48"/>
       <c r="D51" s="48"/>
       <c r="E51" s="48"/>
       <c r="F51" s="48"/>
     </row>
-    <row r="52" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.5"/>
+    <row r="53" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="2" t="s">
         <v>138</v>
       </c>
@@ -7750,7 +7764,7 @@
       </c>
       <c r="G54" s="48"/>
     </row>
-    <row r="55" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="2" t="s">
         <v>133</v>
       </c>
@@ -7769,18 +7783,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B56" s="10"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A57" s="3"/>
       <c r="B57" s="10"/>
     </row>
-    <row r="58" spans="1:7" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:7" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C58" s="13">
         <f>SUM(C47:C57)</f>
         <v>0</v>
@@ -7798,29 +7812,29 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:7" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
     </row>
-    <row r="60" spans="1:7" ht="26" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C60" s="337" t="s">
+    <row r="60" spans="1:7" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C60" s="340" t="s">
         <v>158</v>
       </c>
-      <c r="D60" s="338"/>
-      <c r="E60" s="338"/>
-      <c r="F60" s="339"/>
-    </row>
-    <row r="61" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D60" s="341"/>
+      <c r="E60" s="341"/>
+      <c r="F60" s="342"/>
+    </row>
+    <row r="61" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="44" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A63" s="3" t="s">
         <v>78</v>
       </c>
@@ -7842,13 +7856,13 @@
       </c>
       <c r="G63" s="6"/>
     </row>
-    <row r="64" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="3" t="s">
         <v>134</v>
       </c>
@@ -7870,20 +7884,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B66" s="10"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B67" s="10"/>
     </row>
-    <row r="68" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="2" t="s">
         <v>135</v>
       </c>
@@ -7902,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A69" s="2" t="str">
         <f>A19</f>
         <v>Closing Stock</v>
@@ -7925,7 +7939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="2" t="s">
         <v>4</v>
       </c>
@@ -7948,7 +7962,7 @@
       </c>
       <c r="G70" s="6"/>
     </row>
-    <row r="71" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="2" t="s">
         <v>66</v>
       </c>
@@ -7970,10 +7984,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B72" s="10"/>
     </row>
-    <row r="73" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C73" s="13">
         <f>SUM(C63:C72)</f>
         <v>0</v>
@@ -7991,7 +8005,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="30.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:14" ht="30.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C74" s="7">
         <f>C58-C73</f>
         <v>0</v>
@@ -8009,19 +8023,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7"/>
     </row>
-    <row r="76" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="C76" s="337" t="s">
+    <row r="76" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C76" s="340" t="s">
         <v>158</v>
       </c>
-      <c r="D76" s="338"/>
-      <c r="E76" s="338"/>
-      <c r="F76" s="339"/>
+      <c r="D76" s="341"/>
+      <c r="E76" s="341"/>
+      <c r="F76" s="342"/>
       <c r="H76" s="138"/>
       <c r="I76" s="138"/>
       <c r="J76" s="138"/>
@@ -8030,7 +8044,7 @@
       <c r="M76" s="138"/>
       <c r="N76" s="139"/>
     </row>
-    <row r="77" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="77" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -8043,15 +8057,15 @@
       <c r="M77" s="138"/>
       <c r="N77" s="139"/>
     </row>
-    <row r="78" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A78" s="341" t="s">
+    <row r="78" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="338" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="341"/>
-      <c r="C78" s="341"/>
-      <c r="D78" s="341"/>
-      <c r="E78" s="341"/>
-      <c r="F78" s="341"/>
+      <c r="B78" s="338"/>
+      <c r="C78" s="338"/>
+      <c r="D78" s="338"/>
+      <c r="E78" s="338"/>
+      <c r="F78" s="338"/>
       <c r="H78" s="138"/>
       <c r="I78" s="138"/>
       <c r="J78" s="138"/>
@@ -8060,7 +8074,7 @@
       <c r="M78" s="138"/>
       <c r="N78" s="139"/>
     </row>
-    <row r="79" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="58"/>
       <c r="B79" s="58"/>
       <c r="C79" s="59">
@@ -8080,8 +8094,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:14" ht="26.4" thickTop="1" x14ac:dyDescent="0.5"/>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A81" s="2" t="s">
         <v>69</v>
       </c>
@@ -8104,7 +8118,7 @@
       </c>
       <c r="G81" s="6"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A82" s="2" t="s">
         <v>157</v>
       </c>
@@ -8127,7 +8141,7 @@
       </c>
       <c r="G82" s="6"/>
     </row>
-    <row r="83" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A83" s="2" t="s">
         <v>70</v>
       </c>
@@ -8153,7 +8167,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A84" s="2" t="s">
         <v>74</v>
       </c>
@@ -8178,7 +8192,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A85" s="2" t="s">
         <v>156</v>
       </c>
@@ -8203,16 +8217,16 @@
       <c r="J85" s="87"/>
       <c r="K85" s="87"/>
     </row>
-    <row r="86" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="89" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C89" s="51">
         <f>SUM(C81:C87)</f>
         <v>-10759250</v>
@@ -8230,32 +8244,32 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:12" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C90" s="3"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
     </row>
-    <row r="91" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C91" s="337" t="s">
+    <row r="91" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C91" s="340" t="s">
         <v>158</v>
       </c>
-      <c r="D91" s="338"/>
-      <c r="E91" s="338"/>
-      <c r="F91" s="339"/>
+      <c r="D91" s="341"/>
+      <c r="E91" s="341"/>
+      <c r="F91" s="342"/>
       <c r="I91" s="6"/>
     </row>
-    <row r="92" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="341" t="s">
+    <row r="92" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A92" s="338" t="s">
         <v>204</v>
       </c>
-      <c r="B92" s="341"/>
-      <c r="C92" s="341"/>
-      <c r="D92" s="341"/>
-      <c r="E92" s="341"/>
-      <c r="F92" s="341"/>
-    </row>
-    <row r="93" spans="1:12" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B92" s="338"/>
+      <c r="C92" s="338"/>
+      <c r="D92" s="338"/>
+      <c r="E92" s="338"/>
+      <c r="F92" s="338"/>
+    </row>
+    <row r="93" spans="1:12" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="58"/>
       <c r="B93" s="58"/>
       <c r="C93" s="59">
@@ -8275,13 +8289,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:12" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
     </row>
-    <row r="95" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A95" s="2" t="s">
         <v>130</v>
       </c>
@@ -8303,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A96" s="2" t="s">
         <v>198</v>
       </c>
@@ -8324,19 +8338,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C97" s="48"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
     </row>
-    <row r="98" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C98" s="48"/>
       <c r="D98" s="53"/>
       <c r="E98" s="53"/>
       <c r="F98" s="53"/>
     </row>
-    <row r="99" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C99" s="52">
         <f>SUM(C95:C98)</f>
         <v>0</v>
@@ -8354,28 +8368,28 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C101" s="337" t="s">
+    <row r="101" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C101" s="340" t="s">
         <v>158</v>
       </c>
-      <c r="D101" s="338"/>
-      <c r="E101" s="338"/>
-      <c r="F101" s="339"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D101" s="341"/>
+      <c r="E101" s="341"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A103" s="176" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A104" s="176"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A105" s="2" t="s">
         <v>259</v>
       </c>
@@ -8396,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A107" s="2" t="s">
         <v>260</v>
       </c>
@@ -8420,7 +8434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A108" s="2" t="s">
         <v>4</v>
       </c>
@@ -8444,7 +8458,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A110" s="3" t="s">
         <v>261</v>
       </c>
@@ -8468,6 +8482,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A40:F40"/>
@@ -8475,18 +8501,6 @@
     <mergeCell ref="C60:F60"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C101:F101"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="C76:F76"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.39370078740157483" bottom="0.3" header="0.23622047244094491" footer="0.16"/>
@@ -8503,24 +8517,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr defaultColWidth="21.81640625" defaultRowHeight="25.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="74.54296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27.26953125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="74.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" style="2" customWidth="1"/>
     <col min="5" max="5" width="31" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="21.81640625" style="2"/>
+    <col min="6" max="16384" width="21.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="345"/>
-      <c r="B1" s="345"/>
-      <c r="C1" s="345"/>
-      <c r="D1" s="345"/>
-      <c r="E1" s="345"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A1" s="339"/>
+      <c r="B1" s="339"/>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A2" s="351" t="s">
         <v>214</v>
       </c>
@@ -8529,17 +8543,17 @@
       <c r="D2" s="351"/>
       <c r="E2" s="351"/>
     </row>
-    <row r="3" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="345"/>
-      <c r="B3" s="345"/>
-      <c r="C3" s="345"/>
-      <c r="D3" s="345"/>
-      <c r="E3" s="345"/>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
-      <c r="N3" s="350"/>
-    </row>
-    <row r="4" spans="1:19" ht="57" customHeight="1" x14ac:dyDescent="1">
+    <row r="3" spans="1:19" ht="29.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="339"/>
+      <c r="B3" s="339"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="L3" s="337"/>
+      <c r="M3" s="337"/>
+      <c r="N3" s="337"/>
+    </row>
+    <row r="4" spans="1:19" ht="57" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A4" s="352" t="s">
         <v>221</v>
       </c>
@@ -8550,7 +8564,7 @@
       <c r="F4" s="173"/>
       <c r="G4" s="132"/>
     </row>
-    <row r="5" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="347" t="s">
         <v>0</v>
       </c>
@@ -8571,7 +8585,7 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:19" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="353"/>
       <c r="B6" s="57">
         <f>Assumptions.1!I17</f>
@@ -8591,7 +8605,7 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:19" s="3" customFormat="1" ht="39.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:19" s="3" customFormat="1" ht="38.4" thickTop="1" x14ac:dyDescent="0.5">
       <c r="B7" s="178" t="s">
         <v>225</v>
       </c>
@@ -8605,226 +8619,226 @@
         <v>224</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A8" s="176" t="s">
         <v>219</v>
       </c>
       <c r="B8" s="176"/>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:19" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:19" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="378">
         <f>wp!C11</f>
         <v>0</v>
       </c>
-      <c r="C9" s="6" t="e">
+      <c r="C9" s="378" t="e">
         <f>wp!D11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D9" s="6" t="e">
+      <c r="D9" s="378" t="e">
         <f>wp!E11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E9" s="6" t="e">
+      <c r="E9" s="378" t="e">
         <f>wp!F11</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="379">
         <f>wp!C18</f>
         <v>10759250</v>
       </c>
-      <c r="C10" s="48" t="e">
+      <c r="C10" s="379" t="e">
         <f>wp!D18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D10" s="48" t="e">
+      <c r="D10" s="379" t="e">
         <f>wp!E18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E10" s="48" t="e">
+      <c r="E10" s="379" t="e">
         <f>wp!F18</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K10"/>
       <c r="S10" s="6"/>
     </row>
-    <row r="11" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B11" s="50">
+      <c r="B11" s="380">
         <f>wp!C19</f>
         <v>0</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="380">
         <f>wp!D19</f>
         <v>0</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="380">
         <f>wp!E19</f>
         <v>0</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="380">
         <f>wp!F19</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="378">
         <f>wp!C24</f>
         <v>0</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="378">
         <f>wp!D24</f>
         <v>0</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="378">
         <f>wp!E24</f>
         <v>0</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="378">
         <f>wp!F24</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="378">
         <f>wp!C81</f>
         <v>0</v>
       </c>
-      <c r="C13" s="6" t="e">
+      <c r="C13" s="378" t="e">
         <f>wp!D81</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D13" s="6" t="e">
+      <c r="D13" s="378" t="e">
         <f>wp!E81</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E13" s="6" t="e">
+      <c r="E13" s="378" t="e">
         <f>wp!F81</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="378">
         <f>wp!C82</f>
         <v>0</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="378">
         <f>wp!D82</f>
         <v>0</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="378">
         <f>wp!E82</f>
         <v>0</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="378">
         <f>wp!F82</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="378">
         <f>wp!C83</f>
         <v>0</v>
       </c>
-      <c r="C15" s="6" t="e">
+      <c r="C15" s="378" t="e">
         <f>wp!D83</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D15" s="6" t="e">
+      <c r="D15" s="378" t="e">
         <f>wp!E83</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E15" s="6" t="e">
+      <c r="E15" s="378" t="e">
         <f>wp!F83</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:19" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="378">
         <f>wp!C85</f>
         <v>-10759250</v>
       </c>
-      <c r="C16" s="6" t="e">
+      <c r="C16" s="378" t="e">
         <f>wp!D85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D16" s="6" t="e">
+      <c r="D16" s="378" t="e">
         <f>wp!E85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E16" s="6" t="e">
+      <c r="E16" s="378" t="e">
         <f>wp!F85</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="48">
+      <c r="B17" s="379">
         <f>wp!C95</f>
         <v>0</v>
       </c>
-      <c r="C17" s="48" t="e">
+      <c r="C17" s="379" t="e">
         <f>B17*C22/B22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="379">
         <f>IF(C22=0,0,C17*D22/C22)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="379">
         <f>IF(D22=0,0,D17*E22/D22)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B18" s="48">
+      <c r="B18" s="379">
         <f>wp!C96</f>
         <v>0</v>
       </c>
-      <c r="C18" s="48" t="e">
+      <c r="C18" s="379" t="e">
         <f>wp!D96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D18" s="48" t="e">
+      <c r="D18" s="379" t="e">
         <f>wp!E96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E18" s="48" t="e">
+      <c r="E18" s="379" t="e">
         <f>wp!F96</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2" t="s">
         <v>291</v>
       </c>
@@ -8845,14 +8859,14 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="176" t="s">
         <v>223</v>
       </c>
@@ -8861,142 +8875,142 @@
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B22" s="48">
+      <c r="B22" s="379">
         <f>wp!C50</f>
         <v>0</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="379">
         <f>wp!D50</f>
         <v>0</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="379">
         <f>wp!E50</f>
         <v>0</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="379">
         <f>wp!F50</f>
         <v>0</v>
       </c>
       <c r="F22" s="50"/>
     </row>
-    <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="379">
         <f>wp!C55</f>
         <v>0</v>
       </c>
-      <c r="C23" s="48">
+      <c r="C23" s="379">
         <f>wp!D55</f>
         <v>0</v>
       </c>
-      <c r="D23" s="48">
+      <c r="D23" s="379">
         <f>wp!E55</f>
         <v>0</v>
       </c>
-      <c r="E23" s="48">
+      <c r="E23" s="379">
         <f>wp!F55</f>
         <v>0</v>
       </c>
       <c r="G23" s="175"/>
     </row>
-    <row r="24" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="378">
         <f>wp!C65</f>
         <v>0</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="378">
         <f>wp!D65</f>
         <v>0</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="378">
         <f>wp!E65</f>
         <v>0</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="378">
         <f>wp!F65</f>
         <v>0</v>
       </c>
       <c r="G24" s="175"/>
     </row>
-    <row r="25" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="378">
         <f>wp!C68</f>
         <v>0</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="378">
         <f>wp!D68</f>
         <v>0</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="378">
         <f>wp!E68</f>
         <v>0</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="378">
         <f>wp!F68</f>
         <v>0</v>
       </c>
       <c r="G25" s="175"/>
     </row>
-    <row r="26" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="378">
         <f>wp!C70</f>
         <v>0</v>
       </c>
-      <c r="C26" s="6" t="e">
+      <c r="C26" s="378" t="e">
         <f>wp!D70</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D26" s="6" t="e">
+      <c r="D26" s="378" t="e">
         <f>wp!E70</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E26" s="6" t="e">
+      <c r="E26" s="378" t="e">
         <f>wp!F70</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="378">
         <f>wp!C71</f>
         <v>0</v>
       </c>
-      <c r="C27" s="6" t="e">
+      <c r="C27" s="378" t="e">
         <f>wp!D71</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D27" s="6" t="e">
+      <c r="D27" s="378" t="e">
         <f>wp!E71</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E27" s="6" t="e">
+      <c r="E27" s="378" t="e">
         <f>wp!F71</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C28" s="48"/>
       <c r="D28" s="48"/>
       <c r="E28" s="48"/>
     </row>
-    <row r="29" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="176" t="s">
         <v>222</v>
       </c>
@@ -9004,7 +9018,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="2" t="s">
         <v>226</v>
       </c>
@@ -9025,7 +9039,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A31" s="2" t="s">
         <v>227</v>
       </c>
@@ -9046,7 +9060,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A32" s="2" t="s">
         <v>228</v>
       </c>
@@ -9067,7 +9081,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
         <v>205</v>
       </c>
@@ -9088,7 +9102,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A34" s="2" t="s">
         <v>229</v>
       </c>
@@ -9109,13 +9123,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B35" s="87"/>
       <c r="C35" s="87"/>
       <c r="D35" s="87"/>
       <c r="E35" s="87"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A36" s="176" t="s">
         <v>287</v>
       </c>
@@ -9124,88 +9138,88 @@
       <c r="D36" s="87"/>
       <c r="E36" s="87"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A37" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B37" s="87"/>
-      <c r="C37" s="6" t="e">
+      <c r="B37" s="381"/>
+      <c r="C37" s="378" t="e">
         <f>'MPBF '!B28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D37" s="6" t="e">
+      <c r="D37" s="378" t="e">
         <f>'MPBF '!C28</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E37" s="6" t="e">
+      <c r="E37" s="378" t="e">
         <f>'MPBF '!D28</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A38" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="6" t="e">
+      <c r="B38" s="381"/>
+      <c r="C38" s="378" t="e">
         <f>'MPBF '!B62</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D38" s="6" t="e">
+      <c r="D38" s="378" t="e">
         <f>'MPBF '!C62</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E38" s="6" t="e">
+      <c r="E38" s="378" t="e">
         <f>'MPBF '!D62</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A39" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B39" s="87"/>
-      <c r="C39" s="6" t="e">
+      <c r="B39" s="381"/>
+      <c r="C39" s="378" t="e">
         <f>nayak!C23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D39" s="6" t="e">
+      <c r="D39" s="378" t="e">
         <f>nayak!D23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E39" s="6" t="e">
+      <c r="E39" s="378" t="e">
         <f>nayak!E23</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B40" s="87"/>
       <c r="C40" s="87"/>
       <c r="D40" s="87"/>
       <c r="E40" s="87"/>
     </row>
-    <row r="41" spans="1:5" ht="26" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:5" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
     </row>
-    <row r="42" spans="1:5" ht="26" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:5" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B43" s="354"/>
       <c r="C43" s="355"/>
     </row>
-    <row r="44" spans="1:5" ht="26" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:5" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="356"/>
       <c r="C44" s="357"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="345"/>
-      <c r="B46" s="345"/>
-      <c r="C46" s="345"/>
-      <c r="D46" s="345"/>
-      <c r="E46" s="345"/>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A46" s="339"/>
+      <c r="B46" s="339"/>
+      <c r="C46" s="339"/>
+      <c r="D46" s="339"/>
+      <c r="E46" s="339"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -9226,27 +9240,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:V38"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="23" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="23.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="69" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" style="69" customWidth="1"/>
-    <col min="3" max="3" width="6.81640625" style="69" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" style="69" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="69" customWidth="1"/>
+    <col min="3" max="3" width="6.77734375" style="69" customWidth="1"/>
     <col min="4" max="4" width="11" style="69" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" style="69" customWidth="1"/>
-    <col min="6" max="6" width="11.7265625" style="69" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="69" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" style="69" customWidth="1"/>
-    <col min="9" max="12" width="9.1796875" style="69"/>
+    <col min="5" max="5" width="10.5546875" style="69" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" style="69" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="69" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="69" customWidth="1"/>
+    <col min="9" max="12" width="9.21875" style="69"/>
     <col min="13" max="13" width="6" style="69" customWidth="1"/>
-    <col min="14" max="14" width="5.54296875" style="69" customWidth="1"/>
-    <col min="15" max="20" width="9.1796875" style="69"/>
-    <col min="21" max="21" width="73.1796875" style="69" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="32.453125" style="69" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.1796875" style="69"/>
+    <col min="14" max="14" width="5.5546875" style="69" customWidth="1"/>
+    <col min="15" max="20" width="9.21875" style="69"/>
+    <col min="21" max="21" width="73.21875" style="69" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="32.44140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.21875" style="69"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:22" ht="24" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B2" s="71"/>
       <c r="C2" s="72"/>
       <c r="D2" s="72"/>
@@ -9260,7 +9274,7 @@
       <c r="L2" s="72"/>
       <c r="M2" s="73"/>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B3" s="74"/>
       <c r="C3" s="75"/>
       <c r="D3" s="75"/>
@@ -9274,25 +9288,25 @@
       <c r="L3" s="75"/>
       <c r="M3" s="76"/>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B4" s="74"/>
       <c r="C4" s="75"/>
       <c r="L4" s="75"/>
       <c r="M4" s="76"/>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B5" s="74"/>
       <c r="C5" s="75"/>
       <c r="L5" s="75"/>
       <c r="M5" s="76"/>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B6" s="74"/>
       <c r="C6" s="75"/>
       <c r="L6" s="75"/>
       <c r="M6" s="76"/>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B7" s="74"/>
       <c r="C7" s="75"/>
       <c r="D7" s="358" t="s">
@@ -9311,13 +9325,13 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B8" s="74"/>
       <c r="C8" s="75"/>
       <c r="L8" s="75"/>
       <c r="M8" s="76"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B9" s="74"/>
       <c r="C9" s="75"/>
       <c r="D9" s="358" t="s">
@@ -9333,7 +9347,7 @@
       <c r="L9" s="244"/>
       <c r="M9" s="76"/>
     </row>
-    <row r="10" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="74"/>
       <c r="C10" s="75"/>
       <c r="D10" s="68"/>
@@ -9353,7 +9367,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="11" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="74"/>
       <c r="C11" s="75"/>
       <c r="D11" s="358">
@@ -9372,7 +9386,7 @@
       <c r="U11" s="241"/>
       <c r="V11" s="241"/>
     </row>
-    <row r="12" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="74"/>
       <c r="C12" s="75"/>
       <c r="L12" s="75"/>
@@ -9384,7 +9398,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="2:22" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:22" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="74"/>
       <c r="C13" s="75"/>
       <c r="D13" s="358">
@@ -9407,7 +9421,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="74"/>
       <c r="C14" s="75"/>
       <c r="L14" s="75"/>
@@ -9419,7 +9433,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B15" s="74"/>
       <c r="C15" s="75"/>
       <c r="D15" s="149"/>
@@ -9439,13 +9453,13 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B16" s="74"/>
       <c r="C16" s="75"/>
       <c r="L16" s="75"/>
       <c r="M16" s="76"/>
     </row>
-    <row r="17" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="74"/>
       <c r="C17" s="75"/>
       <c r="D17" s="360">
@@ -9462,7 +9476,7 @@
       <c r="L17" s="243"/>
       <c r="M17" s="78"/>
     </row>
-    <row r="18" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="74"/>
       <c r="C18" s="75"/>
       <c r="D18" s="360"/>
@@ -9476,7 +9490,7 @@
       <c r="L18" s="243"/>
       <c r="M18" s="78"/>
     </row>
-    <row r="19" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="74"/>
       <c r="C19" s="75"/>
       <c r="D19" s="360"/>
@@ -9490,7 +9504,7 @@
       <c r="L19" s="243"/>
       <c r="M19" s="78"/>
     </row>
-    <row r="20" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="74"/>
       <c r="C20" s="75"/>
       <c r="D20" s="360"/>
@@ -9504,7 +9518,7 @@
       <c r="L20" s="243"/>
       <c r="M20" s="78"/>
     </row>
-    <row r="21" spans="2:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="74"/>
       <c r="C21" s="75"/>
       <c r="D21" s="359">
@@ -9521,7 +9535,7 @@
       <c r="L21" s="246"/>
       <c r="M21" s="76"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" s="74"/>
       <c r="C22" s="75"/>
       <c r="D22" s="359"/>
@@ -9535,7 +9549,7 @@
       <c r="L22" s="247"/>
       <c r="M22" s="76"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B23" s="74"/>
       <c r="C23" s="75"/>
       <c r="D23" s="150"/>
@@ -9549,7 +9563,7 @@
       <c r="L23" s="247"/>
       <c r="M23" s="76"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B24" s="74"/>
       <c r="C24" s="75"/>
       <c r="D24" s="150"/>
@@ -9563,7 +9577,7 @@
       <c r="L24" s="247"/>
       <c r="M24" s="76"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="74"/>
       <c r="C25" s="75"/>
       <c r="E25" s="361"/>
@@ -9576,7 +9590,7 @@
       <c r="L25" s="244"/>
       <c r="M25" s="76"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B26" s="74"/>
       <c r="C26" s="75"/>
       <c r="D26" s="358" t="s">
@@ -9595,7 +9609,7 @@
       <c r="L26" s="244"/>
       <c r="M26" s="76"/>
     </row>
-    <row r="27" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="74"/>
       <c r="C27" s="75"/>
       <c r="E27" s="68"/>
@@ -9605,7 +9619,7 @@
       <c r="L27" s="75"/>
       <c r="M27" s="78"/>
     </row>
-    <row r="28" spans="2:13" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:13" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B28" s="74"/>
       <c r="C28" s="75"/>
       <c r="E28" s="70"/>
@@ -9616,13 +9630,13 @@
       <c r="L28" s="75"/>
       <c r="M28" s="76"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B29" s="74"/>
       <c r="C29" s="75"/>
       <c r="L29" s="75"/>
       <c r="M29" s="76"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B30" s="74"/>
       <c r="C30" s="75"/>
       <c r="D30" s="362" t="s">
@@ -9638,7 +9652,7 @@
       <c r="L30" s="248"/>
       <c r="M30" s="76"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B31" s="74"/>
       <c r="C31" s="75"/>
       <c r="E31" s="68"/>
@@ -9651,7 +9665,7 @@
       <c r="L31" s="249"/>
       <c r="M31" s="76"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B32" s="74"/>
       <c r="C32" s="75"/>
       <c r="D32" s="358" t="s">
@@ -9667,7 +9681,7 @@
       <c r="L32" s="244"/>
       <c r="M32" s="76"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B33" s="74"/>
       <c r="C33" s="75"/>
       <c r="D33" s="358" t="s">
@@ -9683,7 +9697,7 @@
       <c r="L33" s="244"/>
       <c r="M33" s="76"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B34" s="74"/>
       <c r="C34" s="75"/>
       <c r="D34" s="358" t="s">
@@ -9699,7 +9713,7 @@
       <c r="L34" s="250"/>
       <c r="M34" s="76"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B35" s="74"/>
       <c r="C35" s="75"/>
       <c r="E35" s="68"/>
@@ -9712,13 +9726,13 @@
       <c r="L35" s="249"/>
       <c r="M35" s="76"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B36" s="74"/>
       <c r="C36" s="75"/>
       <c r="L36" s="75"/>
       <c r="M36" s="76"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B37" s="74"/>
       <c r="C37" s="75"/>
       <c r="D37" s="75"/>
@@ -9732,7 +9746,7 @@
       <c r="L37" s="75"/>
       <c r="M37" s="76"/>
     </row>
-    <row r="38" spans="2:13" ht="23.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:13" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B38" s="77"/>
       <c r="C38" s="80"/>
       <c r="D38" s="80"/>
@@ -9748,11 +9762,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="D32:K32"/>
-    <mergeCell ref="D33:K33"/>
     <mergeCell ref="D34:K34"/>
     <mergeCell ref="D21:K22"/>
     <mergeCell ref="D13:K13"/>
@@ -9761,6 +9770,11 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="D26:G26"/>
     <mergeCell ref="D30:K30"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="D32:K32"/>
+    <mergeCell ref="D33:K33"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.17" top="0.47" bottom="0.42" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="83" orientation="portrait" r:id="rId1"/>
@@ -9770,52 +9784,52 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:V98"/>
-  <sheetFormatPr defaultColWidth="21.81640625" defaultRowHeight="25.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="68" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.81640625" style="2" customWidth="1"/>
-    <col min="3" max="5" width="21.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="2" customWidth="1"/>
+    <col min="3" max="5" width="21.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="21.81640625" style="2"/>
+    <col min="7" max="16384" width="21.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="345">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A1" s="339">
         <f>Assumptions.1!I4</f>
         <v>0</v>
       </c>
-      <c r="B1" s="345"/>
-      <c r="C1" s="345"/>
-      <c r="D1" s="345"/>
-      <c r="E1" s="345"/>
-      <c r="F1" s="345"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="345">
+      <c r="B1" s="339"/>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
+      <c r="F1" s="339"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="A2" s="339">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B2" s="345"/>
-      <c r="C2" s="345"/>
-      <c r="D2" s="345"/>
-      <c r="E2" s="345"/>
-      <c r="F2" s="345"/>
-    </row>
-    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="345">
+      <c r="B2" s="339"/>
+      <c r="C2" s="339"/>
+      <c r="D2" s="339"/>
+      <c r="E2" s="339"/>
+      <c r="F2" s="339"/>
+    </row>
+    <row r="3" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="339">
         <f>Assumptions.1!I7</f>
         <v>0</v>
       </c>
-      <c r="B3" s="345"/>
-      <c r="C3" s="345"/>
-      <c r="D3" s="345"/>
-      <c r="E3" s="345"/>
-      <c r="F3" s="345"/>
-      <c r="M3" s="350"/>
-      <c r="N3" s="350"/>
-      <c r="O3" s="350"/>
-    </row>
-    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="1">
+      <c r="B3" s="339"/>
+      <c r="C3" s="339"/>
+      <c r="D3" s="339"/>
+      <c r="E3" s="339"/>
+      <c r="F3" s="339"/>
+      <c r="M3" s="337"/>
+      <c r="N3" s="337"/>
+      <c r="O3" s="337"/>
+    </row>
+    <row r="4" spans="1:15" ht="57" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A4" s="363" t="s">
         <v>7</v>
       </c>
@@ -9826,11 +9840,11 @@
       <c r="F4" s="363"/>
       <c r="H4" s="132"/>
     </row>
-    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="347" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="342" t="s">
+      <c r="B5" s="343" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="89" t="str">
@@ -9850,9 +9864,9 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:15" ht="59.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="353"/>
-      <c r="B6" s="344"/>
+      <c r="B6" s="345"/>
       <c r="C6" s="57">
         <f>Assumptions.1!I17</f>
         <v>0</v>
@@ -9871,10 +9885,10 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" s="3" customFormat="1" ht="26.4" thickTop="1" x14ac:dyDescent="0.5">
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" ht="31" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:15" s="3" customFormat="1" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
         <v>296</v>
       </c>
@@ -9882,12 +9896,12 @@
       <c r="E8" s="145"/>
       <c r="F8" s="145"/>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A9" s="5"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
         <v>297</v>
       </c>
@@ -9909,7 +9923,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="6"/>
@@ -9917,7 +9931,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C12" s="7">
         <f>SUM(C10:C11)</f>
         <v>0</v>
@@ -9935,15 +9949,15 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -9965,7 +9979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:22" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
         <v>93</v>
       </c>
@@ -9989,7 +10003,7 @@
       <c r="L17"/>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
         <v>292</v>
       </c>
@@ -10011,7 +10025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>67</v>
       </c>
@@ -10032,12 +10046,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:22" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="5"/>
       <c r="C20" s="3"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:22" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>176</v>
       </c>
@@ -10063,10 +10077,10 @@
       <c r="K21" s="82"/>
       <c r="L21" s="82"/>
     </row>
-    <row r="22" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
         <v>177</v>
       </c>
@@ -10088,7 +10102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:22" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="2"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -10096,7 +10110,7 @@
       <c r="F24" s="7"/>
       <c r="V24"/>
     </row>
-    <row r="25" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
         <v>231</v>
       </c>
@@ -10125,7 +10139,7 @@
       <c r="K25" s="86"/>
       <c r="L25" s="86"/>
     </row>
-    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B26" s="11"/>
       <c r="H26" s="83"/>
       <c r="I26" s="83"/>
@@ -10133,7 +10147,7 @@
       <c r="K26" s="83"/>
       <c r="L26" s="83"/>
     </row>
-    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="5" t="s">
         <v>178</v>
       </c>
@@ -10160,7 +10174,7 @@
       <c r="K27" s="83"/>
       <c r="L27" s="83"/>
     </row>
-    <row r="28" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="3"/>
       <c r="B28" s="11"/>
       <c r="H28" s="86"/>
@@ -10169,7 +10183,7 @@
       <c r="K28" s="86"/>
       <c r="L28" s="86"/>
     </row>
-    <row r="29" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="2" t="s">
         <v>179</v>
       </c>
@@ -10196,7 +10210,7 @@
       <c r="K29" s="83"/>
       <c r="L29" s="83"/>
     </row>
-    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B30" s="11"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -10208,7 +10222,7 @@
       <c r="K30" s="83"/>
       <c r="L30" s="83"/>
     </row>
-    <row r="31" spans="1:22" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:22" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="5" t="s">
         <v>180</v>
       </c>
@@ -10234,7 +10248,7 @@
       <c r="K31" s="84"/>
       <c r="L31" s="84"/>
     </row>
-    <row r="32" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="3"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -10245,7 +10259,7 @@
       <c r="K32" s="83"/>
       <c r="L32" s="83"/>
     </row>
-    <row r="33" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
         <v>181</v>
       </c>
@@ -10274,14 +10288,14 @@
       <c r="K33" s="83"/>
       <c r="L33" s="83"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.5">
       <c r="H34" s="83"/>
       <c r="I34" s="83"/>
       <c r="J34" s="83"/>
       <c r="K34" s="83"/>
       <c r="L34" s="83"/>
     </row>
-    <row r="35" spans="1:18" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="8" t="s">
         <v>182</v>
       </c>
@@ -10308,11 +10322,11 @@
       <c r="K35" s="85"/>
       <c r="L35" s="85"/>
     </row>
-    <row r="36" spans="1:18" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="1:18" ht="26" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:18" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -10320,46 +10334,46 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.5">
       <c r="C38" s="126"/>
       <c r="D38" s="126"/>
       <c r="E38" s="126"/>
       <c r="F38" s="126"/>
     </row>
-    <row r="39" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="345">
+    <row r="39" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A39" s="339">
         <f>A1</f>
         <v>0</v>
       </c>
-      <c r="B39" s="345"/>
-      <c r="C39" s="345"/>
-      <c r="D39" s="345"/>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
-    </row>
-    <row r="40" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="345">
+      <c r="B39" s="339"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
+    </row>
+    <row r="40" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="339">
         <f>A2</f>
         <v>0</v>
       </c>
-      <c r="B40" s="345"/>
-      <c r="C40" s="345"/>
-      <c r="D40" s="345"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
-    </row>
-    <row r="41" spans="1:18" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="345">
+      <c r="B40" s="339"/>
+      <c r="C40" s="339"/>
+      <c r="D40" s="339"/>
+      <c r="E40" s="339"/>
+      <c r="F40" s="339"/>
+    </row>
+    <row r="41" spans="1:18" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="339">
         <f>A3</f>
         <v>0</v>
       </c>
-      <c r="B41" s="345"/>
-      <c r="C41" s="345"/>
-      <c r="D41" s="345"/>
-      <c r="E41" s="345"/>
-      <c r="F41" s="345"/>
-    </row>
-    <row r="42" spans="1:18" ht="44.25" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B41" s="339"/>
+      <c r="C41" s="339"/>
+      <c r="D41" s="339"/>
+      <c r="E41" s="339"/>
+      <c r="F41" s="339"/>
+    </row>
+    <row r="42" spans="1:18" ht="44.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -10368,7 +10382,7 @@
       <c r="F42" s="1"/>
       <c r="N42" s="106"/>
     </row>
-    <row r="43" spans="1:18" ht="48.75" customHeight="1" x14ac:dyDescent="1">
+    <row r="43" spans="1:18" ht="48.75" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A43" s="363" t="s">
         <v>10</v>
       </c>
@@ -10379,11 +10393,11 @@
       <c r="F43" s="363"/>
       <c r="H43" s="132"/>
     </row>
-    <row r="44" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="342" t="s">
+    <row r="44" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A44" s="343" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="342" t="s">
+      <c r="B44" s="343" t="s">
         <v>37</v>
       </c>
       <c r="C44" s="89" t="str">
@@ -10403,9 +10417,9 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="343"/>
-      <c r="B45" s="343"/>
+    <row r="45" spans="1:18" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A45" s="344"/>
+      <c r="B45" s="344"/>
       <c r="C45" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10423,26 +10437,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="344"/>
-      <c r="B46" s="344"/>
+    <row r="46" spans="1:18" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="345"/>
+      <c r="B46" s="345"/>
       <c r="C46" s="57"/>
       <c r="D46" s="57"/>
       <c r="E46" s="57"/>
       <c r="F46" s="57"/>
       <c r="R46"/>
     </row>
-    <row r="47" spans="1:18" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="A47" s="44" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="31" x14ac:dyDescent="0.7">
+    <row r="48" spans="1:18" ht="30.6" x14ac:dyDescent="0.55000000000000004">
       <c r="D48" s="145"/>
       <c r="E48" s="145"/>
       <c r="F48" s="145"/>
     </row>
-    <row r="49" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="2" t="s">
         <v>298</v>
       </c>
@@ -10466,20 +10480,20 @@
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
     </row>
-    <row r="50" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="56" t="s">
         <v>77</v>
       </c>
       <c r="B50" s="10"/>
       <c r="J50"/>
     </row>
-    <row r="51" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A51" s="3" t="s">
         <v>75</v>
       </c>
       <c r="B51" s="10"/>
     </row>
-    <row r="52" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A52" s="2" t="s">
         <v>131</v>
       </c>
@@ -10502,20 +10516,20 @@
       </c>
       <c r="G52" s="50"/>
     </row>
-    <row r="53" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B53" s="10"/>
       <c r="C53" s="48"/>
       <c r="D53" s="48"/>
       <c r="E53" s="48"/>
       <c r="F53" s="48"/>
     </row>
-    <row r="54" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="2" t="s">
         <v>138</v>
       </c>
@@ -10538,7 +10552,7 @@
       </c>
       <c r="G55" s="48"/>
     </row>
-    <row r="56" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="2" t="s">
         <v>133</v>
       </c>
@@ -10560,14 +10574,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B57" s="10"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:10" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:10" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C58" s="13">
         <f>C72</f>
         <v>0</v>
@@ -10585,21 +10599,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:10" ht="26.4" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C59" s="69"/>
       <c r="D59" s="69"/>
       <c r="E59" s="69"/>
       <c r="F59" s="69"/>
     </row>
-    <row r="60" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A60" s="44" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A62" s="3" t="s">
         <v>78</v>
       </c>
@@ -10621,13 +10635,13 @@
       </c>
       <c r="G62" s="6"/>
     </row>
-    <row r="63" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A64" s="3" t="s">
         <v>134</v>
       </c>
@@ -10649,14 +10663,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B65" s="10"/>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="3" t="s">
         <v>79</v>
       </c>
@@ -10666,7 +10680,7 @@
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="2" t="s">
         <v>135</v>
       </c>
@@ -10688,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="2" t="str">
         <f>A18</f>
         <v>Closing Stock / WIP</v>
@@ -10711,7 +10725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A69" s="2" t="s">
         <v>4</v>
       </c>
@@ -10734,7 +10748,7 @@
       </c>
       <c r="G69" s="6"/>
     </row>
-    <row r="70" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="2" t="s">
         <v>66</v>
       </c>
@@ -10756,14 +10770,14 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B71" s="10"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:14" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C72" s="13">
         <f>SUM(C62:C71)</f>
         <v>0</v>
@@ -10781,13 +10795,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="30.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:14" ht="30.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7"/>
     </row>
-    <row r="74" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:14" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="146"/>
@@ -10795,7 +10809,7 @@
       <c r="E74" s="146"/>
       <c r="F74" s="146"/>
     </row>
-    <row r="75" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="75" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
@@ -10808,7 +10822,7 @@
       <c r="M75" s="143"/>
       <c r="N75" s="144"/>
     </row>
-    <row r="76" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="76" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="363" t="s">
         <v>38</v>
       </c>
@@ -10825,7 +10839,7 @@
       <c r="M76" s="143"/>
       <c r="N76" s="144"/>
     </row>
-    <row r="77" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:14" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="58"/>
       <c r="B77" s="58"/>
       <c r="C77" s="59">
@@ -10845,8 +10859,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="26" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:14" ht="26.4" thickTop="1" x14ac:dyDescent="0.5"/>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A79" s="2" t="s">
         <v>69</v>
       </c>
@@ -10869,7 +10883,7 @@
       </c>
       <c r="G79" s="6"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A80" s="2" t="s">
         <v>157</v>
       </c>
@@ -10892,7 +10906,7 @@
       </c>
       <c r="G80" s="6"/>
     </row>
-    <row r="81" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A81" s="2" t="s">
         <v>70</v>
       </c>
@@ -10918,7 +10932,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A82" s="2" t="s">
         <v>74</v>
       </c>
@@ -10944,7 +10958,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A83" s="2" t="s">
         <v>293</v>
       </c>
@@ -10969,16 +10983,16 @@
       <c r="J83" s="87"/>
       <c r="K83" s="87"/>
     </row>
-    <row r="84" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="87" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C87" s="52">
         <f>SUM(C79:C86)</f>
         <v>-10759250</v>
@@ -10996,13 +11010,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C88" s="3"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
     </row>
-    <row r="89" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A89" s="363" t="s">
         <v>39</v>
       </c>
@@ -11012,7 +11026,7 @@
       <c r="E89" s="363"/>
       <c r="F89" s="363"/>
     </row>
-    <row r="90" spans="1:12" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:12" ht="98.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="58"/>
       <c r="B90" s="58"/>
       <c r="C90" s="59">
@@ -11032,13 +11046,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:12" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
     </row>
-    <row r="92" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A92" s="2" t="s">
         <v>199</v>
       </c>
@@ -11060,7 +11074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A93" s="2" t="s">
         <v>299</v>
       </c>
@@ -11082,19 +11096,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C94" s="48"/>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C95" s="48"/>
       <c r="D95" s="53"/>
       <c r="E95" s="53"/>
       <c r="F95" s="53"/>
     </row>
-    <row r="96" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C96" s="52">
         <f>SUM(C91:C95)</f>
         <v>0</v>
@@ -11112,12 +11126,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="3:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="3:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="3:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C98" s="69"/>
       <c r="D98" s="69"/>
       <c r="E98" s="69"/>
@@ -11125,11 +11139,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A76:F76"/>
@@ -11140,6 +11149,11 @@
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.56000000000000005" right="0.15748031496062992" top="0.31496062992125984" bottom="0.38" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="52" orientation="portrait" r:id="rId1"/>
@@ -11152,17 +11166,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I106"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.54296875" style="18" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="18" customWidth="1"/>
-    <col min="3" max="5" width="12.453125" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" style="18" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="18"/>
+    <col min="1" max="1" width="27.5546875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="18" customWidth="1"/>
+    <col min="3" max="5" width="12.44140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="18" customWidth="1"/>
+    <col min="8" max="16384" width="9.21875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="364">
         <f>Assumptions.1!I4</f>
         <v>0</v>
@@ -11174,7 +11188,7 @@
       <c r="F1" s="364"/>
       <c r="G1" s="41"/>
     </row>
-    <row r="2" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="364">
         <f>Assumptions.1!I6</f>
         <v>0</v>
@@ -11186,7 +11200,7 @@
       <c r="F2" s="364"/>
       <c r="G2" s="41"/>
     </row>
-    <row r="3" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="364">
         <f>Assumptions.1!I7</f>
         <v>0</v>
@@ -11198,7 +11212,7 @@
       <c r="F3" s="364"/>
       <c r="G3" s="41"/>
     </row>
-    <row r="5" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="365" t="s">
         <v>20</v>
       </c>
@@ -11260,7 +11274,7 @@
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E10" s="35"/>
       <c r="G10" s="17"/>
     </row>
@@ -11342,7 +11356,7 @@
       <c r="E15" s="33"/>
       <c r="G15" s="17"/>
     </row>
-    <row r="16" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="22" t="s">
         <v>60</v>
       </c>
@@ -11399,7 +11413,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A21" s="25"/>
       <c r="B21" s="28"/>
       <c r="C21" s="26"/>
@@ -11481,7 +11495,7 @@
       </c>
       <c r="B29" s="372"/>
     </row>
-    <row r="31" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
         <v>14</v>
       </c>
@@ -11561,7 +11575,7 @@
       <c r="E38" s="27"/>
       <c r="G38" s="17"/>
     </row>
-    <row r="39" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="34" t="s">
         <v>58</v>
       </c>
@@ -11572,18 +11586,18 @@
       <c r="F39" s="22"/>
       <c r="G39" s="17"/>
     </row>
-    <row r="40" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E40" s="35"/>
       <c r="G40" s="17"/>
     </row>
-    <row r="41" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A41" s="252" t="s">
         <v>252</v>
       </c>
       <c r="E41" s="35"/>
       <c r="G41" s="17"/>
     </row>
-    <row r="42" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A42" s="37"/>
       <c r="E42" s="35"/>
       <c r="G42" s="17"/>
@@ -11611,7 +11625,7 @@
       </c>
       <c r="G43" s="17"/>
     </row>
-    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E44" s="35"/>
       <c r="G44" s="17"/>
     </row>
@@ -11643,7 +11657,7 @@
       <c r="E46" s="27"/>
       <c r="G46" s="17"/>
     </row>
-    <row r="47" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="34" t="s">
         <v>59</v>
       </c>
@@ -11776,7 +11790,7 @@
       <c r="D57" s="27"/>
       <c r="E57" s="27"/>
     </row>
-    <row r="58" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="22" t="s">
         <v>63</v>
       </c>
@@ -11905,7 +11919,7 @@
       <c r="E67" s="17"/>
       <c r="G67" s="17"/>
     </row>
-    <row r="68" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="368" t="s">
         <v>56</v>
       </c>
@@ -11962,7 +11976,7 @@
       </c>
       <c r="G72" s="17"/>
     </row>
-    <row r="73" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.35">
       <c r="A73" s="25"/>
       <c r="C73" s="26"/>
       <c r="D73" s="26"/>
@@ -12042,7 +12056,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="366" t="s">
         <v>13</v>
       </c>
@@ -12140,7 +12154,7 @@
       <c r="D88" s="17"/>
       <c r="E88" s="17"/>
     </row>
-    <row r="89" spans="1:7" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="366" t="s">
         <v>55</v>
       </c>
@@ -12154,13 +12168,13 @@
       <c r="D90" s="17"/>
       <c r="E90" s="17"/>
     </row>
-    <row r="91" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A91" s="252" t="s">
         <v>256</v>
       </c>
       <c r="E91" s="35"/>
     </row>
-    <row r="92" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A92" s="37"/>
       <c r="E92" s="35"/>
     </row>
@@ -12187,7 +12201,7 @@
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E94" s="35"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -12217,7 +12231,7 @@
       <c r="D96" s="27"/>
       <c r="E96" s="27"/>
     </row>
-    <row r="97" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:6" ht="16.8" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="22" t="s">
         <v>61</v>
       </c>
@@ -12227,7 +12241,7 @@
       <c r="E97" s="36"/>
       <c r="F97" s="22"/>
     </row>
-    <row r="98" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E98" s="35"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
@@ -12278,7 +12292,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="22" t="s">
         <v>62</v>
       </c>
@@ -12288,7 +12302,7 @@
       <c r="E105" s="22"/>
       <c r="F105" s="22"/>
     </row>
-    <row r="106" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="E106" s="35"/>
     </row>
   </sheetData>
@@ -12323,16 +12337,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D65"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.453125" style="38" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" style="38" customWidth="1"/>
-    <col min="4" max="4" width="14.1796875" style="38" customWidth="1"/>
-    <col min="5" max="16384" width="9.1796875" style="38"/>
+    <col min="1" max="1" width="44.44140625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="38" customWidth="1"/>
+    <col min="3" max="4" width="14.21875" style="38" customWidth="1"/>
+    <col min="5" max="16384" width="9.21875" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="364">
         <f>Assumptions.1!I4</f>
         <v>0</v>
@@ -12341,7 +12354,7 @@
       <c r="C1" s="364"/>
       <c r="D1" s="364"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="364">
         <f>Assumptions.1!I6</f>
         <v>0</v>
@@ -12350,7 +12363,7 @@
       <c r="C2" s="364"/>
       <c r="D2" s="364"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="364">
         <f>Assumptions.1!I7</f>
         <v>0</v>
@@ -12359,7 +12372,7 @@
       <c r="C3" s="364"/>
       <c r="D3" s="364"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="365" t="s">
         <v>51</v>
       </c>
@@ -12367,12 +12380,12 @@
       <c r="C5" s="365"/>
       <c r="D5" s="365"/>
     </row>
-    <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A7" s="140" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="127" t="s">
         <v>23</v>
       </c>
@@ -12389,7 +12402,7 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="129"/>
       <c r="B9" s="130">
         <f>wp!D6</f>
@@ -12404,12 +12417,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
     </row>
-    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="38" t="s">
         <v>42</v>
       </c>
@@ -12426,12 +12439,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
     </row>
-    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
         <v>43</v>
       </c>
@@ -12448,13 +12461,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="38" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
         <v>45</v>
       </c>
@@ -12471,17 +12484,17 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
     </row>
-    <row r="18" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
         <v>53</v>
       </c>
@@ -12498,12 +12511,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="s">
         <v>46</v>
       </c>
@@ -12520,12 +12533,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B23" s="43"/>
       <c r="C23" s="43"/>
       <c r="D23" s="43"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="38" t="s">
         <v>47</v>
       </c>
@@ -12542,12 +12555,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" s="43"/>
       <c r="C25" s="43"/>
       <c r="D25" s="43"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
         <v>48</v>
       </c>
@@ -12564,12 +12577,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B27" s="43"/>
       <c r="C27" s="43"/>
       <c r="D27" s="43"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="40" t="s">
         <v>49</v>
       </c>
@@ -12586,7 +12599,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="40" t="s">
         <v>50</v>
       </c>
@@ -12594,18 +12607,18 @@
       <c r="C29" s="40"/>
       <c r="D29" s="40"/>
     </row>
-    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="55"/>
       <c r="B30" s="55"/>
       <c r="C30" s="55"/>
       <c r="D30" s="55"/>
     </row>
-    <row r="42" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A42" s="140" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="127" t="s">
         <v>23</v>
       </c>
@@ -12622,7 +12635,7 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="129"/>
       <c r="B44" s="130">
         <f t="shared" si="0"/>
@@ -12637,12 +12650,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B45" s="42"/>
       <c r="C45" s="42"/>
       <c r="D45" s="42"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="38" t="s">
         <v>42</v>
       </c>
@@ -12659,12 +12672,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47" s="43"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="38" t="s">
         <v>43</v>
       </c>
@@ -12681,12 +12694,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="38" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="38" t="s">
         <v>45</v>
       </c>
@@ -12703,17 +12716,17 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B52" s="43"/>
       <c r="C52" s="43"/>
       <c r="D52" s="43"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="38" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="38" t="s">
         <v>71</v>
       </c>
@@ -12730,7 +12743,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="38" t="s">
         <v>46</v>
       </c>
@@ -12747,12 +12760,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B57" s="43"/>
       <c r="C57" s="43"/>
       <c r="D57" s="43"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="38" t="s">
         <v>47</v>
       </c>
@@ -12769,12 +12782,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59" s="43"/>
       <c r="C59" s="43"/>
       <c r="D59" s="43"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="38" t="s">
         <v>48</v>
       </c>
@@ -12791,12 +12804,12 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" s="43"/>
       <c r="C61" s="43"/>
       <c r="D61" s="43"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="40" t="s">
         <v>49</v>
       </c>
@@ -12813,7 +12826,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="40" t="s">
         <v>50</v>
       </c>
@@ -12821,7 +12834,7 @@
       <c r="C63" s="40"/>
       <c r="D63" s="40"/>
     </row>
-    <row r="65" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="55"/>
       <c r="B65" s="55"/>
       <c r="C65" s="55"/>
@@ -12842,18 +12855,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.1796875" style="38" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" style="38" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" style="38" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" style="38" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" style="38" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="38"/>
+    <col min="1" max="1" width="27.21875" style="38" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="38" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="38" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="38" customWidth="1"/>
+    <col min="6" max="16384" width="9.21875" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="364">
         <f>Assumptions.1!I4</f>
         <v>0</v>
@@ -12863,7 +12876,7 @@
       <c r="D2" s="364"/>
       <c r="E2" s="364"/>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="364">
         <f>Assumptions.1!I6</f>
         <v>0</v>
@@ -12873,7 +12886,7 @@
       <c r="D3" s="364"/>
       <c r="E3" s="364"/>
     </row>
-    <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="364">
         <f>Assumptions.1!I7</f>
         <v>0</v>
@@ -12883,7 +12896,7 @@
       <c r="D4" s="364"/>
       <c r="E4" s="364"/>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="365" t="s">
         <v>82</v>
       </c>
@@ -12892,11 +12905,11 @@
       <c r="D6" s="365"/>
       <c r="E6" s="365"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="40"/>
       <c r="B7" s="40"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="364" t="s">
         <v>83</v>
       </c>
@@ -12905,7 +12918,7 @@
       <c r="D8" s="364"/>
       <c r="E8" s="364"/>
     </row>
-    <row r="10" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="127" t="s">
         <v>0</v>
       </c>
@@ -12923,7 +12936,7 @@
         <v>Projected</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="129"/>
       <c r="B11" s="130"/>
       <c r="C11" s="130">
@@ -12939,8 +12952,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="s">
         <v>41</v>
       </c>
@@ -12958,10 +12971,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="43"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="38" t="s">
         <v>266</v>
       </c>
@@ -12979,16 +12992,16 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="s">
         <v>84</v>
       </c>
       <c r="B16" s="43"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B17" s="43"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="38" t="s">
         <v>264</v>
       </c>
@@ -13006,16 +13019,16 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="s">
         <v>265</v>
       </c>
       <c r="B19" s="43"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B20" s="43"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
         <v>85</v>
       </c>
@@ -13033,10 +13046,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" s="43"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="s">
         <v>86</v>
       </c>
@@ -13054,24 +13067,24 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="55"/>
       <c r="B24" s="55"/>
       <c r="C24" s="55"/>
       <c r="D24" s="55"/>
       <c r="E24" s="55"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="40" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="38" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="38" t="s">
         <v>89</v>
       </c>
@@ -13092,13 +13105,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:M94"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" style="18" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="18" customWidth="1"/>
     <col min="3" max="12" width="11" style="18" customWidth="1"/>
-    <col min="13" max="13" width="11.453125" style="18" customWidth="1"/>
-    <col min="14" max="16384" width="9.1796875" style="18"/>
+    <col min="13" max="13" width="11.44140625" style="18" customWidth="1"/>
+    <col min="14" max="16384" width="9.21875" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -13288,7 +13301,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="96"/>
       <c r="B12" s="97">
         <f>Assumptions.1!I65</f>
@@ -13336,7 +13349,7 @@
       </c>
       <c r="M12" s="98"/>
     </row>
-    <row r="13" spans="1:13" ht="14" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B13" s="99"/>
       <c r="C13" s="99"/>
       <c r="D13" s="99"/>
@@ -14221,7 +14234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="22"/>
       <c r="B35" s="299"/>
       <c r="C35" s="299"/>
